--- a/Results/regression_results_pivot.xlsx
+++ b/Results/regression_results_pivot.xlsx
@@ -4836,7 +4836,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_FLD_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
@@ -4870,7 +4870,7 @@
       <c r="AD57" s="2" t="inlineStr"/>
       <c r="AE57" s="2" t="inlineStr">
         <is>
-          <t>-0.0045**</t>
+          <t>-0.0073**</t>
         </is>
       </c>
       <c r="AF57" s="2" t="inlineStr"/>
@@ -4919,7 +4919,7 @@
       <c r="AD58" s="2" t="inlineStr"/>
       <c r="AE58" s="2" t="inlineStr">
         <is>
-          <t>(0.0020)</t>
+          <t>(0.0035)</t>
         </is>
       </c>
       <c r="AF58" s="2" t="inlineStr"/>
@@ -4938,7 +4938,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_3_HAZARDS_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
@@ -4970,7 +4970,11 @@
       <c r="AB59" s="2" t="inlineStr"/>
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr"/>
-      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr">
+        <is>
+          <t>0.0038*</t>
+        </is>
+      </c>
       <c r="AF59" s="2" t="inlineStr"/>
       <c r="AG59" s="2" t="inlineStr"/>
       <c r="AH59" s="2" t="inlineStr"/>
@@ -4979,11 +4983,7 @@
       <c r="AK59" s="2" t="inlineStr"/>
       <c r="AL59" s="2" t="inlineStr"/>
       <c r="AM59" s="2" t="inlineStr"/>
-      <c r="AN59" s="2" t="inlineStr">
-        <is>
-          <t>-0.0017</t>
-        </is>
-      </c>
+      <c r="AN59" s="2" t="inlineStr"/>
       <c r="AO59" s="2" t="inlineStr"/>
       <c r="AP59" s="2" t="inlineStr"/>
       <c r="AQ59" s="2" t="inlineStr"/>
@@ -5019,7 +5019,11 @@
       <c r="AB60" s="2" t="inlineStr"/>
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr"/>
-      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr">
+        <is>
+          <t>(0.0020)</t>
+        </is>
+      </c>
       <c r="AF60" s="2" t="inlineStr"/>
       <c r="AG60" s="2" t="inlineStr"/>
       <c r="AH60" s="2" t="inlineStr"/>
@@ -5028,11 +5032,7 @@
       <c r="AK60" s="2" t="inlineStr"/>
       <c r="AL60" s="2" t="inlineStr"/>
       <c r="AM60" s="2" t="inlineStr"/>
-      <c r="AN60" s="2" t="inlineStr">
-        <is>
-          <t>(0.0015)</t>
-        </is>
-      </c>
+      <c r="AN60" s="2" t="inlineStr"/>
       <c r="AO60" s="2" t="inlineStr"/>
       <c r="AP60" s="2" t="inlineStr"/>
       <c r="AQ60" s="2" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_STM_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
@@ -5074,7 +5074,7 @@
       <c r="AD61" s="2" t="inlineStr"/>
       <c r="AE61" s="2" t="inlineStr">
         <is>
-          <t>0.0038*</t>
+          <t>-0.0045**</t>
         </is>
       </c>
       <c r="AF61" s="2" t="inlineStr"/>
@@ -5142,7 +5142,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_EQK_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_3_HAZARDS_per_POP</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
@@ -5174,11 +5174,7 @@
       <c r="AB63" s="2" t="inlineStr"/>
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr"/>
-      <c r="AE63" s="2" t="inlineStr">
-        <is>
-          <t>-0.0073**</t>
-        </is>
-      </c>
+      <c r="AE63" s="2" t="inlineStr"/>
       <c r="AF63" s="2" t="inlineStr"/>
       <c r="AG63" s="2" t="inlineStr"/>
       <c r="AH63" s="2" t="inlineStr"/>
@@ -5187,7 +5183,11 @@
       <c r="AK63" s="2" t="inlineStr"/>
       <c r="AL63" s="2" t="inlineStr"/>
       <c r="AM63" s="2" t="inlineStr"/>
-      <c r="AN63" s="2" t="inlineStr"/>
+      <c r="AN63" s="2" t="inlineStr">
+        <is>
+          <t>-0.0017</t>
+        </is>
+      </c>
       <c r="AO63" s="2" t="inlineStr"/>
       <c r="AP63" s="2" t="inlineStr"/>
       <c r="AQ63" s="2" t="inlineStr"/>
@@ -5223,11 +5223,7 @@
       <c r="AB64" s="2" t="inlineStr"/>
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr"/>
-      <c r="AE64" s="2" t="inlineStr">
-        <is>
-          <t>(0.0035)</t>
-        </is>
-      </c>
+      <c r="AE64" s="2" t="inlineStr"/>
       <c r="AF64" s="2" t="inlineStr"/>
       <c r="AG64" s="2" t="inlineStr"/>
       <c r="AH64" s="2" t="inlineStr"/>
@@ -5236,7 +5232,11 @@
       <c r="AK64" s="2" t="inlineStr"/>
       <c r="AL64" s="2" t="inlineStr"/>
       <c r="AM64" s="2" t="inlineStr"/>
-      <c r="AN64" s="2" t="inlineStr"/>
+      <c r="AN64" s="2" t="inlineStr">
+        <is>
+          <t>(0.0015)</t>
+        </is>
+      </c>
       <c r="AO64" s="2" t="inlineStr"/>
       <c r="AP64" s="2" t="inlineStr"/>
       <c r="AQ64" s="2" t="inlineStr"/>
@@ -5244,7 +5244,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C_log_GDP:C_log_DIS_EQK_per_POP</t>
+          <t>C_log_GDP:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
@@ -5279,7 +5279,7 @@
       <c r="AE65" s="2" t="inlineStr"/>
       <c r="AF65" s="2" t="inlineStr">
         <is>
-          <t>0.0946***</t>
+          <t>-0.0659**</t>
         </is>
       </c>
       <c r="AG65" s="2" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
       <c r="AE66" s="2" t="inlineStr"/>
       <c r="AF66" s="2" t="inlineStr">
         <is>
-          <t>(0.0284)</t>
+          <t>(0.0301)</t>
         </is>
       </c>
       <c r="AG66" s="2" t="inlineStr"/>
@@ -5346,7 +5346,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C_log_GDP:C_log_DIS_STM_per_POP</t>
+          <t>C_log_GDP:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       <c r="AE67" s="2" t="inlineStr"/>
       <c r="AF67" s="2" t="inlineStr">
         <is>
-          <t>-0.0659**</t>
+          <t>0.0210</t>
         </is>
       </c>
       <c r="AG67" s="2" t="inlineStr"/>
@@ -5430,7 +5430,7 @@
       <c r="AE68" s="2" t="inlineStr"/>
       <c r="AF68" s="2" t="inlineStr">
         <is>
-          <t>(0.0301)</t>
+          <t>(0.0294)</t>
         </is>
       </c>
       <c r="AG68" s="2" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C_log_GDP:C_log_DIS_FLD_per_POP</t>
+          <t>C_log_GDP:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
@@ -5585,7 +5585,7 @@
       <c r="AE71" s="2" t="inlineStr"/>
       <c r="AF71" s="2" t="inlineStr">
         <is>
-          <t>0.0210</t>
+          <t>0.0946***</t>
         </is>
       </c>
       <c r="AG71" s="2" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
       <c r="AE72" s="2" t="inlineStr"/>
       <c r="AF72" s="2" t="inlineStr">
         <is>
-          <t>(0.0294)</t>
+          <t>(0.0284)</t>
         </is>
       </c>
       <c r="AG72" s="2" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_FLD_per_POP</t>
+          <t>C_CWGI:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       <c r="AF73" s="2" t="inlineStr"/>
       <c r="AG73" s="2" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>-0.1155***</t>
         </is>
       </c>
       <c r="AH73" s="2" t="inlineStr"/>
@@ -5737,7 +5737,7 @@
       <c r="AF74" s="2" t="inlineStr"/>
       <c r="AG74" s="2" t="inlineStr">
         <is>
-          <t>(0.0482)</t>
+          <t>(0.0390)</t>
         </is>
       </c>
       <c r="AH74" s="2" t="inlineStr"/>
@@ -5754,7 +5754,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_EQK_per_POP</t>
+          <t>C_CWGI:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
@@ -5790,7 +5790,7 @@
       <c r="AF75" s="2" t="inlineStr"/>
       <c r="AG75" s="2" t="inlineStr">
         <is>
-          <t>0.0671*</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="AH75" s="2" t="inlineStr"/>
@@ -5839,7 +5839,7 @@
       <c r="AF76" s="2" t="inlineStr"/>
       <c r="AG76" s="2" t="inlineStr">
         <is>
-          <t>(0.0376)</t>
+          <t>(0.0482)</t>
         </is>
       </c>
       <c r="AH76" s="2" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_STM_per_POP</t>
+          <t>C_CWGI:C_log_DIS_3_HAZARDS_per_POP</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
@@ -5890,11 +5890,7 @@
       <c r="AD77" s="2" t="inlineStr"/>
       <c r="AE77" s="2" t="inlineStr"/>
       <c r="AF77" s="2" t="inlineStr"/>
-      <c r="AG77" s="2" t="inlineStr">
-        <is>
-          <t>-0.1155***</t>
-        </is>
-      </c>
+      <c r="AG77" s="2" t="inlineStr"/>
       <c r="AH77" s="2" t="inlineStr"/>
       <c r="AI77" s="2" t="inlineStr"/>
       <c r="AJ77" s="2" t="inlineStr"/>
@@ -5903,7 +5899,11 @@
       <c r="AM77" s="2" t="inlineStr"/>
       <c r="AN77" s="2" t="inlineStr"/>
       <c r="AO77" s="2" t="inlineStr"/>
-      <c r="AP77" s="2" t="inlineStr"/>
+      <c r="AP77" s="2" t="inlineStr">
+        <is>
+          <t>-0.0262</t>
+        </is>
+      </c>
       <c r="AQ77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
@@ -5939,11 +5939,7 @@
       <c r="AD78" s="2" t="inlineStr"/>
       <c r="AE78" s="2" t="inlineStr"/>
       <c r="AF78" s="2" t="inlineStr"/>
-      <c r="AG78" s="2" t="inlineStr">
-        <is>
-          <t>(0.0390)</t>
-        </is>
-      </c>
+      <c r="AG78" s="2" t="inlineStr"/>
       <c r="AH78" s="2" t="inlineStr"/>
       <c r="AI78" s="2" t="inlineStr"/>
       <c r="AJ78" s="2" t="inlineStr"/>
@@ -5952,13 +5948,17 @@
       <c r="AM78" s="2" t="inlineStr"/>
       <c r="AN78" s="2" t="inlineStr"/>
       <c r="AO78" s="2" t="inlineStr"/>
-      <c r="AP78" s="2" t="inlineStr"/>
+      <c r="AP78" s="2" t="inlineStr">
+        <is>
+          <t>(0.0258)</t>
+        </is>
+      </c>
       <c r="AQ78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_3_HAZARDS_per_POP</t>
+          <t>C_CWGI:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
@@ -5992,7 +5992,11 @@
       <c r="AD79" s="2" t="inlineStr"/>
       <c r="AE79" s="2" t="inlineStr"/>
       <c r="AF79" s="2" t="inlineStr"/>
-      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr">
+        <is>
+          <t>0.0671*</t>
+        </is>
+      </c>
       <c r="AH79" s="2" t="inlineStr"/>
       <c r="AI79" s="2" t="inlineStr"/>
       <c r="AJ79" s="2" t="inlineStr"/>
@@ -6001,11 +6005,7 @@
       <c r="AM79" s="2" t="inlineStr"/>
       <c r="AN79" s="2" t="inlineStr"/>
       <c r="AO79" s="2" t="inlineStr"/>
-      <c r="AP79" s="2" t="inlineStr">
-        <is>
-          <t>-0.0262</t>
-        </is>
-      </c>
+      <c r="AP79" s="2" t="inlineStr"/>
       <c r="AQ79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
@@ -6041,7 +6041,11 @@
       <c r="AD80" s="2" t="inlineStr"/>
       <c r="AE80" s="2" t="inlineStr"/>
       <c r="AF80" s="2" t="inlineStr"/>
-      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr">
+        <is>
+          <t>(0.0376)</t>
+        </is>
+      </c>
       <c r="AH80" s="2" t="inlineStr"/>
       <c r="AI80" s="2" t="inlineStr"/>
       <c r="AJ80" s="2" t="inlineStr"/>
@@ -6050,17 +6054,13 @@
       <c r="AM80" s="2" t="inlineStr"/>
       <c r="AN80" s="2" t="inlineStr"/>
       <c r="AO80" s="2" t="inlineStr"/>
-      <c r="AP80" s="2" t="inlineStr">
-        <is>
-          <t>(0.0258)</t>
-        </is>
-      </c>
+      <c r="AP80" s="2" t="inlineStr"/>
       <c r="AQ80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C_CDBQ:C_log_DIS_STM_per_POP</t>
+          <t>C_CDBQ:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
@@ -6097,7 +6097,7 @@
       <c r="AG81" s="2" t="inlineStr"/>
       <c r="AH81" s="2" t="inlineStr">
         <is>
-          <t>-0.0202***</t>
+          <t>0.0125*</t>
         </is>
       </c>
       <c r="AI81" s="2" t="inlineStr"/>
@@ -6162,7 +6162,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C_CDBQ:C_log_DIS_EQK_per_POP</t>
+          <t>C_CDBQ:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
@@ -6199,7 +6199,7 @@
       <c r="AG83" s="2" t="inlineStr"/>
       <c r="AH83" s="2" t="inlineStr">
         <is>
-          <t>0.0349**</t>
+          <t>-0.0202***</t>
         </is>
       </c>
       <c r="AI83" s="2" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       <c r="AG84" s="2" t="inlineStr"/>
       <c r="AH84" s="2" t="inlineStr">
         <is>
-          <t>(0.0153)</t>
+          <t>(0.0071)</t>
         </is>
       </c>
       <c r="AI84" s="2" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C_CDBQ:C_log_DIS_FLD_per_POP</t>
+          <t>C_CDBQ:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
       <c r="AG85" s="2" t="inlineStr"/>
       <c r="AH85" s="2" t="inlineStr">
         <is>
-          <t>0.0125*</t>
+          <t>0.0349**</t>
         </is>
       </c>
       <c r="AI85" s="2" t="inlineStr"/>
@@ -6350,7 +6350,7 @@
       <c r="AG86" s="2" t="inlineStr"/>
       <c r="AH86" s="2" t="inlineStr">
         <is>
-          <t>(0.0071)</t>
+          <t>(0.0153)</t>
         </is>
       </c>
       <c r="AI86" s="2" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Earthquake Count (per Pop)</t>
+          <t>Storm Count (per Pop)</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
@@ -6497,47 +6497,47 @@
       <c r="Y89" s="2" t="inlineStr"/>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>0.0438</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>0.0501</t>
+          <t>0.0049</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>0.0564</t>
+          <t>0.0087</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>0.0556</t>
+          <t>0.0011</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>0.0501</t>
+          <t>0.0217</t>
         </is>
       </c>
       <c r="AE89" s="2" t="inlineStr">
         <is>
-          <t>0.0215</t>
+          <t>0.0207</t>
         </is>
       </c>
       <c r="AF89" s="2" t="inlineStr">
         <is>
-          <t>0.0376</t>
+          <t>0.0053</t>
         </is>
       </c>
       <c r="AG89" s="2" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0136</t>
         </is>
       </c>
       <c r="AH89" s="2" t="inlineStr">
         <is>
-          <t>0.1278**</t>
+          <t>-0.0259</t>
         </is>
       </c>
       <c r="AI89" s="2" t="inlineStr"/>
@@ -6578,47 +6578,47 @@
       <c r="Y90" s="2" t="inlineStr"/>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>(0.0470)</t>
+          <t>(0.0285)</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>(0.0473)</t>
+          <t>(0.0290)</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>(0.0481)</t>
+          <t>(0.0307)</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>(0.0466)</t>
+          <t>(0.0302)</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>(0.0503)</t>
+          <t>(0.0379)</t>
         </is>
       </c>
       <c r="AE90" s="2" t="inlineStr">
         <is>
-          <t>(0.0381)</t>
+          <t>(0.0254)</t>
         </is>
       </c>
       <c r="AF90" s="2" t="inlineStr">
         <is>
-          <t>(0.0425)</t>
+          <t>(0.0307)</t>
         </is>
       </c>
       <c r="AG90" s="2" t="inlineStr">
         <is>
-          <t>(0.0440)</t>
+          <t>(0.0260)</t>
         </is>
       </c>
       <c r="AH90" s="2" t="inlineStr">
         <is>
-          <t>(0.0590)</t>
+          <t>(0.0386)</t>
         </is>
       </c>
       <c r="AI90" s="2" t="inlineStr"/>
@@ -6634,7 +6634,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Flood Count (per Pop)</t>
+          <t>3 Hazards (per Pop)</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
@@ -6661,60 +6661,60 @@
       <c r="W91" s="2" t="inlineStr"/>
       <c r="X91" s="2" t="inlineStr"/>
       <c r="Y91" s="2" t="inlineStr"/>
-      <c r="Z91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0169</t>
-        </is>
-      </c>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0043</t>
-        </is>
-      </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0048</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0015</t>
-        </is>
-      </c>
-      <c r="AD91" s="2" t="inlineStr">
-        <is>
-          <t>0.0093</t>
-        </is>
-      </c>
-      <c r="AE91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0271</t>
-        </is>
-      </c>
-      <c r="AF91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0257</t>
-        </is>
-      </c>
-      <c r="AG91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0116</t>
-        </is>
-      </c>
-      <c r="AH91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0012</t>
-        </is>
-      </c>
-      <c r="AI91" s="2" t="inlineStr"/>
-      <c r="AJ91" s="2" t="inlineStr"/>
-      <c r="AK91" s="2" t="inlineStr"/>
-      <c r="AL91" s="2" t="inlineStr"/>
-      <c r="AM91" s="2" t="inlineStr"/>
-      <c r="AN91" s="2" t="inlineStr"/>
-      <c r="AO91" s="2" t="inlineStr"/>
-      <c r="AP91" s="2" t="inlineStr"/>
-      <c r="AQ91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr">
+        <is>
+          <t>0.0098</t>
+        </is>
+      </c>
+      <c r="AJ91" s="2" t="inlineStr">
+        <is>
+          <t>0.0222</t>
+        </is>
+      </c>
+      <c r="AK91" s="2" t="inlineStr">
+        <is>
+          <t>0.0257</t>
+        </is>
+      </c>
+      <c r="AL91" s="2" t="inlineStr">
+        <is>
+          <t>0.0211</t>
+        </is>
+      </c>
+      <c r="AM91" s="2" t="inlineStr">
+        <is>
+          <t>0.0459*</t>
+        </is>
+      </c>
+      <c r="AN91" s="2" t="inlineStr">
+        <is>
+          <t>0.0170</t>
+        </is>
+      </c>
+      <c r="AO91" s="2" t="inlineStr">
+        <is>
+          <t>0.0215</t>
+        </is>
+      </c>
+      <c r="AP91" s="2" t="inlineStr">
+        <is>
+          <t>0.0199</t>
+        </is>
+      </c>
+      <c r="AQ91" s="2" t="inlineStr">
+        <is>
+          <t>0.0314</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -6742,65 +6742,65 @@
       <c r="W92" s="2" t="inlineStr"/>
       <c r="X92" s="2" t="inlineStr"/>
       <c r="Y92" s="2" t="inlineStr"/>
-      <c r="Z92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0306)</t>
-        </is>
-      </c>
-      <c r="AA92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0304)</t>
-        </is>
-      </c>
-      <c r="AB92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0307)</t>
-        </is>
-      </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0302)</t>
-        </is>
-      </c>
-      <c r="AD92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0298)</t>
-        </is>
-      </c>
-      <c r="AE92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0281)</t>
-        </is>
-      </c>
-      <c r="AF92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0311)</t>
-        </is>
-      </c>
-      <c r="AG92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0306)</t>
-        </is>
-      </c>
-      <c r="AH92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0327)</t>
-        </is>
-      </c>
-      <c r="AI92" s="2" t="inlineStr"/>
-      <c r="AJ92" s="2" t="inlineStr"/>
-      <c r="AK92" s="2" t="inlineStr"/>
-      <c r="AL92" s="2" t="inlineStr"/>
-      <c r="AM92" s="2" t="inlineStr"/>
-      <c r="AN92" s="2" t="inlineStr"/>
-      <c r="AO92" s="2" t="inlineStr"/>
-      <c r="AP92" s="2" t="inlineStr"/>
-      <c r="AQ92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0201)</t>
+        </is>
+      </c>
+      <c r="AJ92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0208)</t>
+        </is>
+      </c>
+      <c r="AK92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0216)</t>
+        </is>
+      </c>
+      <c r="AL92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0215)</t>
+        </is>
+      </c>
+      <c r="AM92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0268)</t>
+        </is>
+      </c>
+      <c r="AN92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0204)</t>
+        </is>
+      </c>
+      <c r="AO92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0228)</t>
+        </is>
+      </c>
+      <c r="AP92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0197)</t>
+        </is>
+      </c>
+      <c r="AQ92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0266)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Storm Count (per Pop)</t>
+          <t>Flood Count (per Pop)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
@@ -6829,47 +6829,47 @@
       <c r="Y93" s="2" t="inlineStr"/>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>-0.0169</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>0.0049</t>
+          <t>-0.0043</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>0.0087</t>
+          <t>-0.0048</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>0.0011</t>
+          <t>-0.0015</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>0.0217</t>
+          <t>0.0093</t>
         </is>
       </c>
       <c r="AE93" s="2" t="inlineStr">
         <is>
-          <t>0.0207</t>
+          <t>-0.0271</t>
         </is>
       </c>
       <c r="AF93" s="2" t="inlineStr">
         <is>
-          <t>0.0053</t>
+          <t>-0.0257</t>
         </is>
       </c>
       <c r="AG93" s="2" t="inlineStr">
         <is>
-          <t>0.0136</t>
+          <t>-0.0116</t>
         </is>
       </c>
       <c r="AH93" s="2" t="inlineStr">
         <is>
-          <t>-0.0259</t>
+          <t>-0.0012</t>
         </is>
       </c>
       <c r="AI93" s="2" t="inlineStr"/>
@@ -6910,12 +6910,12 @@
       <c r="Y94" s="2" t="inlineStr"/>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>(0.0285)</t>
+          <t>(0.0306)</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>(0.0290)</t>
+          <t>(0.0304)</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -6930,27 +6930,27 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>(0.0379)</t>
+          <t>(0.0298)</t>
         </is>
       </c>
       <c r="AE94" s="2" t="inlineStr">
         <is>
-          <t>(0.0254)</t>
+          <t>(0.0281)</t>
         </is>
       </c>
       <c r="AF94" s="2" t="inlineStr">
         <is>
-          <t>(0.0307)</t>
+          <t>(0.0311)</t>
         </is>
       </c>
       <c r="AG94" s="2" t="inlineStr">
         <is>
-          <t>(0.0260)</t>
+          <t>(0.0306)</t>
         </is>
       </c>
       <c r="AH94" s="2" t="inlineStr">
         <is>
-          <t>(0.0386)</t>
+          <t>(0.0327)</t>
         </is>
       </c>
       <c r="AI94" s="2" t="inlineStr"/>
@@ -6966,7 +6966,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3 Hazards (per Pop)</t>
+          <t>Earthquake Count (per Pop)</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr"/>
@@ -6993,60 +6993,60 @@
       <c r="W95" s="2" t="inlineStr"/>
       <c r="X95" s="2" t="inlineStr"/>
       <c r="Y95" s="2" t="inlineStr"/>
-      <c r="Z95" s="2" t="inlineStr"/>
-      <c r="AA95" s="2" t="inlineStr"/>
-      <c r="AB95" s="2" t="inlineStr"/>
-      <c r="AC95" s="2" t="inlineStr"/>
-      <c r="AD95" s="2" t="inlineStr"/>
-      <c r="AE95" s="2" t="inlineStr"/>
-      <c r="AF95" s="2" t="inlineStr"/>
-      <c r="AG95" s="2" t="inlineStr"/>
-      <c r="AH95" s="2" t="inlineStr"/>
-      <c r="AI95" s="2" t="inlineStr">
-        <is>
-          <t>0.0098</t>
-        </is>
-      </c>
-      <c r="AJ95" s="2" t="inlineStr">
-        <is>
-          <t>0.0222</t>
-        </is>
-      </c>
-      <c r="AK95" s="2" t="inlineStr">
-        <is>
-          <t>0.0257</t>
-        </is>
-      </c>
-      <c r="AL95" s="2" t="inlineStr">
-        <is>
-          <t>0.0211</t>
-        </is>
-      </c>
-      <c r="AM95" s="2" t="inlineStr">
-        <is>
-          <t>0.0459*</t>
-        </is>
-      </c>
-      <c r="AN95" s="2" t="inlineStr">
-        <is>
-          <t>0.0170</t>
-        </is>
-      </c>
-      <c r="AO95" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>0.0438</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0.0501</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0.0564</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>0.0556</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>0.0501</t>
+        </is>
+      </c>
+      <c r="AE95" s="2" t="inlineStr">
         <is>
           <t>0.0215</t>
         </is>
       </c>
-      <c r="AP95" s="2" t="inlineStr">
-        <is>
-          <t>0.0199</t>
-        </is>
-      </c>
-      <c r="AQ95" s="2" t="inlineStr">
-        <is>
-          <t>0.0314</t>
-        </is>
-      </c>
+      <c r="AF95" s="2" t="inlineStr">
+        <is>
+          <t>0.0376</t>
+        </is>
+      </c>
+      <c r="AG95" s="2" t="inlineStr">
+        <is>
+          <t>0.0127</t>
+        </is>
+      </c>
+      <c r="AH95" s="2" t="inlineStr">
+        <is>
+          <t>0.1278**</t>
+        </is>
+      </c>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+      <c r="AK95" s="2" t="inlineStr"/>
+      <c r="AL95" s="2" t="inlineStr"/>
+      <c r="AM95" s="2" t="inlineStr"/>
+      <c r="AN95" s="2" t="inlineStr"/>
+      <c r="AO95" s="2" t="inlineStr"/>
+      <c r="AP95" s="2" t="inlineStr"/>
+      <c r="AQ95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -7074,275 +7074,275 @@
       <c r="W96" s="2" t="inlineStr"/>
       <c r="X96" s="2" t="inlineStr"/>
       <c r="Y96" s="2" t="inlineStr"/>
-      <c r="Z96" s="2" t="inlineStr"/>
-      <c r="AA96" s="2" t="inlineStr"/>
-      <c r="AB96" s="2" t="inlineStr"/>
-      <c r="AC96" s="2" t="inlineStr"/>
-      <c r="AD96" s="2" t="inlineStr"/>
-      <c r="AE96" s="2" t="inlineStr"/>
-      <c r="AF96" s="2" t="inlineStr"/>
-      <c r="AG96" s="2" t="inlineStr"/>
-      <c r="AH96" s="2" t="inlineStr"/>
-      <c r="AI96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0201)</t>
-        </is>
-      </c>
-      <c r="AJ96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0208)</t>
-        </is>
-      </c>
-      <c r="AK96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0216)</t>
-        </is>
-      </c>
-      <c r="AL96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0215)</t>
-        </is>
-      </c>
-      <c r="AM96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0268)</t>
-        </is>
-      </c>
-      <c r="AN96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0204)</t>
-        </is>
-      </c>
-      <c r="AO96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0228)</t>
-        </is>
-      </c>
-      <c r="AP96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0197)</t>
-        </is>
-      </c>
-      <c r="AQ96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0266)</t>
-        </is>
-      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0470)</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0473)</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0481)</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0466)</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0503)</t>
+        </is>
+      </c>
+      <c r="AE96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0381)</t>
+        </is>
+      </c>
+      <c r="AF96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0425)</t>
+        </is>
+      </c>
+      <c r="AG96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0440)</t>
+        </is>
+      </c>
+      <c r="AH96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0590)</t>
+        </is>
+      </c>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+      <c r="AK96" s="2" t="inlineStr"/>
+      <c r="AL96" s="2" t="inlineStr"/>
+      <c r="AM96" s="2" t="inlineStr"/>
+      <c r="AN96" s="2" t="inlineStr"/>
+      <c r="AO96" s="2" t="inlineStr"/>
+      <c r="AP96" s="2" t="inlineStr"/>
+      <c r="AQ96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Region FE: Middle East &amp; North Africa</t>
+          <t>Region FE: Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>0.0927</t>
+          <t>-0.0031</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>0.0644</t>
+          <t>-0.0455</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>0.0536</t>
+          <t>-0.1027**</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>0.0506</t>
+          <t>-0.1025**</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>0.0839</t>
+          <t>-0.0786</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>0.0620</t>
+          <t>-0.0849*</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0.1039</t>
+          <t>-0.0070</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>-0.0727</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>0.0725</t>
+          <t>-0.0727</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>-0.0504</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>0.0780</t>
+          <t>-0.0621</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0.0627</t>
+          <t>-0.0855</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>-0.0698</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>0.1170</t>
+          <t>-0.0422</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0.0795</t>
+          <t>-0.0747</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>0.0779</t>
+          <t>-0.0361</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>0.0632</t>
+          <t>-0.0953*</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>0.0611</t>
+          <t>-0.0953*</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>0.1040</t>
+          <t>-0.0648</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>0.0703</t>
+          <t>-0.0798</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>-0.1050*</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>0.0558</t>
+          <t>-0.1002*</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>0.0968</t>
+          <t>-0.0725</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>0.0674</t>
+          <t>-0.0832</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>-0.0393</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>-0.0874</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>0.0680</t>
+          <t>-0.0810</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>0.0920</t>
+          <t>-0.0668</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>0.0820</t>
+          <t>-0.0548</t>
         </is>
       </c>
       <c r="AE97" s="2" t="inlineStr">
         <is>
-          <t>0.0672</t>
+          <t>-0.0985</t>
         </is>
       </c>
       <c r="AF97" s="2" t="inlineStr">
         <is>
-          <t>0.0616</t>
+          <t>-0.0859</t>
         </is>
       </c>
       <c r="AG97" s="2" t="inlineStr">
         <is>
-          <t>0.0799</t>
+          <t>-0.0716</t>
         </is>
       </c>
       <c r="AH97" s="2" t="inlineStr">
         <is>
-          <t>0.0511</t>
+          <t>-0.1170**</t>
         </is>
       </c>
       <c r="AI97" s="2" t="inlineStr">
         <is>
-          <t>0.0798</t>
+          <t>-0.0349</t>
         </is>
       </c>
       <c r="AJ97" s="2" t="inlineStr">
         <is>
-          <t>0.0874</t>
+          <t>-0.0839</t>
         </is>
       </c>
       <c r="AK97" s="2" t="inlineStr">
         <is>
-          <t>0.0810</t>
+          <t>-0.0802</t>
         </is>
       </c>
       <c r="AL97" s="2" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>-0.0626</t>
         </is>
       </c>
       <c r="AM97" s="2" t="inlineStr">
         <is>
-          <t>0.0930</t>
+          <t>-0.0546</t>
         </is>
       </c>
       <c r="AN97" s="2" t="inlineStr">
         <is>
-          <t>0.0911</t>
+          <t>-0.0833</t>
         </is>
       </c>
       <c r="AO97" s="2" t="inlineStr">
         <is>
-          <t>0.0882</t>
+          <t>-0.0825</t>
         </is>
       </c>
       <c r="AP97" s="2" t="inlineStr">
         <is>
-          <t>0.1089</t>
+          <t>-0.0683</t>
         </is>
       </c>
       <c r="AQ97" s="2" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>-0.0613</t>
         </is>
       </c>
     </row>
@@ -7350,212 +7350,212 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>(0.0771)</t>
+          <t>(0.0525)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>(0.0722)</t>
+          <t>(0.0511)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>(0.0679)</t>
+          <t>(0.0511)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>(0.0716)</t>
+          <t>(0.0514)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>(0.0728)</t>
+          <t>(0.0521)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>(0.0734)</t>
+          <t>(0.0505)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>(0.0749)</t>
+          <t>(0.0501)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>(0.0738)</t>
+          <t>(0.0508)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>(0.0767)</t>
+          <t>(0.0506)</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>(0.0817)</t>
+          <t>(0.0535)</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>(0.0851)</t>
+          <t>(0.0536)</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>(0.0771)</t>
+          <t>(0.0536)</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>(0.0752)</t>
+          <t>(0.0532)</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>(0.0783)</t>
+          <t>(0.0558)</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>(0.0810)</t>
+          <t>(0.0516)</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>(0.0743)</t>
+          <t>(0.0500)</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>(0.0720)</t>
+          <t>(0.0526)</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>(0.0762)</t>
+          <t>(0.0528)</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>(0.0814)</t>
+          <t>(0.0551)</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>(0.0877)</t>
+          <t>(0.0568)</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>(0.0721)</t>
+          <t>(0.0541)</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>(0.0744)</t>
+          <t>(0.0535)</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>(0.0779)</t>
+          <t>(0.0546)</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>(0.0784)</t>
+          <t>(0.0546)</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>(0.0822)</t>
+          <t>(0.0616)</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>(0.0780)</t>
+          <t>(0.0590)</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>(0.0778)</t>
+          <t>(0.0609)</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>(0.0778)</t>
+          <t>(0.0598)</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>(0.0773)</t>
+          <t>(0.0600)</t>
         </is>
       </c>
       <c r="AE98" s="2" t="inlineStr">
         <is>
-          <t>(0.0798)</t>
+          <t>(0.0600)</t>
         </is>
       </c>
       <c r="AF98" s="2" t="inlineStr">
         <is>
-          <t>(0.0753)</t>
+          <t>(0.0577)</t>
         </is>
       </c>
       <c r="AG98" s="2" t="inlineStr">
         <is>
-          <t>(0.0751)</t>
+          <t>(0.0599)</t>
         </is>
       </c>
       <c r="AH98" s="2" t="inlineStr">
         <is>
-          <t>(0.0742)</t>
+          <t>(0.0546)</t>
         </is>
       </c>
       <c r="AI98" s="2" t="inlineStr">
         <is>
-          <t>(0.0821)</t>
+          <t>(0.0595)</t>
         </is>
       </c>
       <c r="AJ98" s="2" t="inlineStr">
         <is>
-          <t>(0.0779)</t>
+          <t>(0.0572)</t>
         </is>
       </c>
       <c r="AK98" s="2" t="inlineStr">
         <is>
-          <t>(0.0782)</t>
+          <t>(0.0587)</t>
         </is>
       </c>
       <c r="AL98" s="2" t="inlineStr">
         <is>
-          <t>(0.0785)</t>
+          <t>(0.0583)</t>
         </is>
       </c>
       <c r="AM98" s="2" t="inlineStr">
         <is>
-          <t>(0.0779)</t>
+          <t>(0.0570)</t>
         </is>
       </c>
       <c r="AN98" s="2" t="inlineStr">
         <is>
-          <t>(0.0793)</t>
+          <t>(0.0579)</t>
         </is>
       </c>
       <c r="AO98" s="2" t="inlineStr">
         <is>
-          <t>(0.0774)</t>
+          <t>(0.0572)</t>
         </is>
       </c>
       <c r="AP98" s="2" t="inlineStr">
         <is>
-          <t>(0.0781)</t>
+          <t>(0.0567)</t>
         </is>
       </c>
       <c r="AQ98" s="2" t="inlineStr">
         <is>
-          <t>(0.0756)</t>
+          <t>(0.0552)</t>
         </is>
       </c>
     </row>
@@ -7992,217 +7992,217 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Region FE: Europe &amp; Central Asia</t>
+          <t>Region FE: Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>-0.0031</t>
+          <t>-0.3124***</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>-0.0455</t>
+          <t>-0.2552***</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>-0.1027**</t>
+          <t>-0.2682***</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>-0.1025**</t>
+          <t>-0.2690***</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-0.0786</t>
+          <t>-0.2558***</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-0.0849*</t>
+          <t>-0.2672***</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>-0.0070</t>
+          <t>-0.1773***</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>-0.0727</t>
+          <t>-0.1999***</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>-0.0727</t>
+          <t>-0.2020***</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-0.0504</t>
+          <t>-0.1914***</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>-0.0621</t>
+          <t>-0.2075***</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-0.0855</t>
+          <t>-0.2314***</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-0.0698</t>
+          <t>-0.2084***</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-0.0422</t>
+          <t>-0.1891***</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>-0.0747</t>
+          <t>-0.2104***</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>-0.0361</t>
+          <t>-0.2447***</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>-0.0953*</t>
+          <t>-0.2607***</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>-0.0953*</t>
+          <t>-0.2614***</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>-0.0648</t>
+          <t>-0.2422***</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>-0.0798</t>
+          <t>-0.2619***</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>-0.1050*</t>
+          <t>-0.2663***</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>-0.1002*</t>
+          <t>-0.2623***</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>-0.0725</t>
+          <t>-0.2422***</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>-0.0832</t>
+          <t>-0.2698***</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
-          <t>-0.0393</t>
+          <t>-0.2498***</t>
         </is>
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>-0.0874</t>
+          <t>-0.2501***</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>-0.0810</t>
+          <t>-0.2489***</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>-0.0668</t>
+          <t>-0.2430***</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>-0.0548</t>
+          <t>-0.2378***</t>
         </is>
       </c>
       <c r="AE101" s="2" t="inlineStr">
         <is>
-          <t>-0.0985</t>
+          <t>-0.2842***</t>
         </is>
       </c>
       <c r="AF101" s="2" t="inlineStr">
         <is>
-          <t>-0.0859</t>
+          <t>-0.2441***</t>
         </is>
       </c>
       <c r="AG101" s="2" t="inlineStr">
         <is>
-          <t>-0.0716</t>
+          <t>-0.2345***</t>
         </is>
       </c>
       <c r="AH101" s="2" t="inlineStr">
         <is>
-          <t>-0.1170**</t>
+          <t>-0.2375***</t>
         </is>
       </c>
       <c r="AI101" s="2" t="inlineStr">
         <is>
-          <t>-0.0349</t>
+          <t>-0.2444***</t>
         </is>
       </c>
       <c r="AJ101" s="2" t="inlineStr">
         <is>
-          <t>-0.0839</t>
+          <t>-0.2450***</t>
         </is>
       </c>
       <c r="AK101" s="2" t="inlineStr">
         <is>
-          <t>-0.0802</t>
+          <t>-0.2444***</t>
         </is>
       </c>
       <c r="AL101" s="2" t="inlineStr">
         <is>
-          <t>-0.0626</t>
+          <t>-0.2369***</t>
         </is>
       </c>
       <c r="AM101" s="2" t="inlineStr">
         <is>
-          <t>-0.0546</t>
+          <t>-0.2346***</t>
         </is>
       </c>
       <c r="AN101" s="2" t="inlineStr">
         <is>
-          <t>-0.0833</t>
+          <t>-0.2666***</t>
         </is>
       </c>
       <c r="AO101" s="2" t="inlineStr">
         <is>
-          <t>-0.0825</t>
+          <t>-0.2401***</t>
         </is>
       </c>
       <c r="AP101" s="2" t="inlineStr">
         <is>
-          <t>-0.0683</t>
+          <t>-0.2200***</t>
         </is>
       </c>
       <c r="AQ101" s="2" t="inlineStr">
         <is>
-          <t>-0.0613</t>
+          <t>-0.2244***</t>
         </is>
       </c>
     </row>
@@ -8210,429 +8210,429 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>(0.0525)</t>
+          <t>(0.0572)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>(0.0511)</t>
+          <t>(0.0547)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>(0.0511)</t>
+          <t>(0.0552)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>(0.0514)</t>
+          <t>(0.0556)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>(0.0521)</t>
+          <t>(0.0530)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>(0.0505)</t>
+          <t>(0.0515)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>(0.0501)</t>
+          <t>(0.0622)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>(0.0508)</t>
+          <t>(0.0652)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>(0.0506)</t>
+          <t>(0.0654)</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>(0.0535)</t>
+          <t>(0.0625)</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>(0.0536)</t>
+          <t>(0.0644)</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>(0.0536)</t>
+          <t>(0.0621)</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>(0.0532)</t>
+          <t>(0.0683)</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>(0.0558)</t>
+          <t>(0.0644)</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>(0.0516)</t>
+          <t>(0.0680)</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>(0.0500)</t>
+          <t>(0.0539)</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>(0.0526)</t>
+          <t>(0.0556)</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>(0.0528)</t>
+          <t>(0.0562)</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>(0.0551)</t>
+          <t>(0.0540)</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>(0.0568)</t>
+          <t>(0.0574)</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>(0.0541)</t>
+          <t>(0.0549)</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>(0.0535)</t>
+          <t>(0.0560)</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>(0.0546)</t>
+          <t>(0.0531)</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>(0.0546)</t>
+          <t>(0.0588)</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>(0.0616)</t>
+          <t>(0.0685)</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>(0.0590)</t>
+          <t>(0.0728)</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>(0.0609)</t>
+          <t>(0.0729)</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>(0.0598)</t>
+          <t>(0.0697)</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>(0.0600)</t>
+          <t>(0.0650)</t>
         </is>
       </c>
       <c r="AE102" s="2" t="inlineStr">
         <is>
-          <t>(0.0600)</t>
+          <t>(0.0729)</t>
         </is>
       </c>
       <c r="AF102" s="2" t="inlineStr">
         <is>
-          <t>(0.0577)</t>
+          <t>(0.0669)</t>
         </is>
       </c>
       <c r="AG102" s="2" t="inlineStr">
         <is>
-          <t>(0.0599)</t>
+          <t>(0.0593)</t>
         </is>
       </c>
       <c r="AH102" s="2" t="inlineStr">
         <is>
-          <t>(0.0546)</t>
+          <t>(0.0569)</t>
         </is>
       </c>
       <c r="AI102" s="2" t="inlineStr">
         <is>
+          <t>(0.0638)</t>
+        </is>
+      </c>
+      <c r="AJ102" s="2" t="inlineStr">
+        <is>
+          <t>(0.0662)</t>
+        </is>
+      </c>
+      <c r="AK102" s="2" t="inlineStr">
+        <is>
+          <t>(0.0658)</t>
+        </is>
+      </c>
+      <c r="AL102" s="2" t="inlineStr">
+        <is>
+          <t>(0.0627)</t>
+        </is>
+      </c>
+      <c r="AM102" s="2" t="inlineStr">
+        <is>
+          <t>(0.0585)</t>
+        </is>
+      </c>
+      <c r="AN102" s="2" t="inlineStr">
+        <is>
+          <t>(0.0669)</t>
+        </is>
+      </c>
+      <c r="AO102" s="2" t="inlineStr">
+        <is>
+          <t>(0.0699)</t>
+        </is>
+      </c>
+      <c r="AP102" s="2" t="inlineStr">
+        <is>
           <t>(0.0595)</t>
         </is>
       </c>
-      <c r="AJ102" s="2" t="inlineStr">
-        <is>
-          <t>(0.0572)</t>
-        </is>
-      </c>
-      <c r="AK102" s="2" t="inlineStr">
-        <is>
-          <t>(0.0587)</t>
-        </is>
-      </c>
-      <c r="AL102" s="2" t="inlineStr">
-        <is>
-          <t>(0.0583)</t>
-        </is>
-      </c>
-      <c r="AM102" s="2" t="inlineStr">
-        <is>
-          <t>(0.0570)</t>
-        </is>
-      </c>
-      <c r="AN102" s="2" t="inlineStr">
-        <is>
-          <t>(0.0579)</t>
-        </is>
-      </c>
-      <c r="AO102" s="2" t="inlineStr">
-        <is>
-          <t>(0.0572)</t>
-        </is>
-      </c>
-      <c r="AP102" s="2" t="inlineStr">
-        <is>
-          <t>(0.0567)</t>
-        </is>
-      </c>
       <c r="AQ102" s="2" t="inlineStr">
         <is>
-          <t>(0.0552)</t>
+          <t>(0.0641)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Region FE: North America</t>
+          <t>Region FE: Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>0.2444***</t>
+          <t>0.0927</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>0.2009***</t>
+          <t>0.0644</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>0.1059*</t>
+          <t>0.0536</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>0.1052</t>
+          <t>0.0506</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>0.1135*</t>
+          <t>0.0839</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>0.0982*</t>
+          <t>0.0620</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>0.2269**</t>
+          <t>0.1039</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>0.1469</t>
+          <t>0.0805</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.0725</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0.1473*</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>0.1414*</t>
+          <t>0.0780</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.0627</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>0.1944*</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>0.2050**</t>
+          <t>0.1170</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>0.1496*</t>
+          <t>0.0795</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>0.1825***</t>
+          <t>0.0779</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>0.0945</t>
+          <t>0.0632</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.0611</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>0.0965</t>
+          <t>0.1040</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>0.0939</t>
+          <t>0.0703</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>0.1060</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0.1231*</t>
+          <t>0.0558</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>0.1171*</t>
+          <t>0.0968</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>0.0901</t>
+          <t>0.0674</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
         <is>
-          <t>0.2097***</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>0.1248*</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>0.1260*</t>
+          <t>0.0680</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>0.1288**</t>
+          <t>0.0920</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>0.1236**</t>
+          <t>0.0820</t>
         </is>
       </c>
       <c r="AE103" s="2" t="inlineStr">
         <is>
-          <t>0.1191*</t>
+          <t>0.0672</t>
         </is>
       </c>
       <c r="AF103" s="2" t="inlineStr">
         <is>
-          <t>0.1399**</t>
+          <t>0.0616</t>
         </is>
       </c>
       <c r="AG103" s="2" t="inlineStr">
         <is>
-          <t>0.1229**</t>
+          <t>0.0799</t>
         </is>
       </c>
       <c r="AH103" s="2" t="inlineStr">
         <is>
-          <t>0.1068*</t>
+          <t>0.0511</t>
         </is>
       </c>
       <c r="AI103" s="2" t="inlineStr">
         <is>
-          <t>0.2137***</t>
+          <t>0.0798</t>
         </is>
       </c>
       <c r="AJ103" s="2" t="inlineStr">
         <is>
-          <t>0.1262*</t>
+          <t>0.0874</t>
         </is>
       </c>
       <c r="AK103" s="2" t="inlineStr">
         <is>
-          <t>0.1267*</t>
+          <t>0.0810</t>
         </is>
       </c>
       <c r="AL103" s="2" t="inlineStr">
         <is>
-          <t>0.1304**</t>
+          <t>0.1057</t>
         </is>
       </c>
       <c r="AM103" s="2" t="inlineStr">
         <is>
-          <t>0.1235**</t>
+          <t>0.0930</t>
         </is>
       </c>
       <c r="AN103" s="2" t="inlineStr">
         <is>
-          <t>0.1286*</t>
+          <t>0.0911</t>
         </is>
       </c>
       <c r="AO103" s="2" t="inlineStr">
         <is>
-          <t>0.1265*</t>
+          <t>0.0882</t>
         </is>
       </c>
       <c r="AP103" s="2" t="inlineStr">
         <is>
-          <t>0.1230**</t>
+          <t>0.1089</t>
         </is>
       </c>
       <c r="AQ103" s="2" t="inlineStr">
         <is>
-          <t>0.1241**</t>
+          <t>0.0832</t>
         </is>
       </c>
     </row>
@@ -8640,429 +8640,429 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>(0.0540)</t>
+          <t>(0.0771)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>(0.0508)</t>
+          <t>(0.0722)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>(0.0641)</t>
+          <t>(0.0679)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>(0.0642)</t>
+          <t>(0.0716)</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>(0.0580)</t>
+          <t>(0.0728)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>(0.0552)</t>
+          <t>(0.0734)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>(0.0941)</t>
+          <t>(0.0749)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>(0.0957)</t>
+          <t>(0.0738)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>(0.0951)</t>
+          <t>(0.0767)</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>(0.0874)</t>
+          <t>(0.0817)</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>(0.0801)</t>
+          <t>(0.0851)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>(0.1023)</t>
+          <t>(0.0771)</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>(0.1056)</t>
+          <t>(0.0752)</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>(0.1001)</t>
+          <t>(0.0783)</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>(0.0807)</t>
+          <t>(0.0810)</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>(0.0637)</t>
+          <t>(0.0743)</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>(0.0704)</t>
+          <t>(0.0720)</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>(0.0705)</t>
+          <t>(0.0762)</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>(0.0646)</t>
+          <t>(0.0814)</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>(0.0584)</t>
+          <t>(0.0877)</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>(0.0692)</t>
+          <t>(0.0721)</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>(0.0713)</t>
+          <t>(0.0744)</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>(0.0678)</t>
+          <t>(0.0779)</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>(0.0616)</t>
+          <t>(0.0784)</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
         <is>
-          <t>(0.0628)</t>
+          <t>(0.0822)</t>
         </is>
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>(0.0692)</t>
+          <t>(0.0780)</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>(0.0685)</t>
+          <t>(0.0778)</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>(0.0618)</t>
+          <t>(0.0778)</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>(0.0581)</t>
+          <t>(0.0773)</t>
         </is>
       </c>
       <c r="AE104" s="2" t="inlineStr">
         <is>
-          <t>(0.0685)</t>
+          <t>(0.0798)</t>
         </is>
       </c>
       <c r="AF104" s="2" t="inlineStr">
         <is>
-          <t>(0.0629)</t>
+          <t>(0.0753)</t>
         </is>
       </c>
       <c r="AG104" s="2" t="inlineStr">
         <is>
-          <t>(0.0554)</t>
+          <t>(0.0751)</t>
         </is>
       </c>
       <c r="AH104" s="2" t="inlineStr">
         <is>
-          <t>(0.0547)</t>
+          <t>(0.0742)</t>
         </is>
       </c>
       <c r="AI104" s="2" t="inlineStr">
         <is>
-          <t>(0.0614)</t>
+          <t>(0.0821)</t>
         </is>
       </c>
       <c r="AJ104" s="2" t="inlineStr">
         <is>
-          <t>(0.0693)</t>
+          <t>(0.0779)</t>
         </is>
       </c>
       <c r="AK104" s="2" t="inlineStr">
         <is>
-          <t>(0.0689)</t>
+          <t>(0.0782)</t>
         </is>
       </c>
       <c r="AL104" s="2" t="inlineStr">
         <is>
-          <t>(0.0628)</t>
+          <t>(0.0785)</t>
         </is>
       </c>
       <c r="AM104" s="2" t="inlineStr">
         <is>
-          <t>(0.0583)</t>
+          <t>(0.0779)</t>
         </is>
       </c>
       <c r="AN104" s="2" t="inlineStr">
         <is>
-          <t>(0.0705)</t>
+          <t>(0.0793)</t>
         </is>
       </c>
       <c r="AO104" s="2" t="inlineStr">
         <is>
-          <t>(0.0696)</t>
+          <t>(0.0774)</t>
         </is>
       </c>
       <c r="AP104" s="2" t="inlineStr">
         <is>
-          <t>(0.0623)</t>
+          <t>(0.0781)</t>
         </is>
       </c>
       <c r="AQ104" s="2" t="inlineStr">
         <is>
-          <t>(0.0618)</t>
+          <t>(0.0756)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Region FE: Sub-Saharan Africa</t>
+          <t>Region FE: South Asia</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>-0.3124***</t>
+          <t>-0.2547**</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>-0.2552***</t>
+          <t>-0.2628**</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-0.2682***</t>
+          <t>-0.2375**</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>-0.2690***</t>
+          <t>-0.2358**</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-0.2558***</t>
+          <t>-0.2271**</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-0.2672***</t>
+          <t>-0.2417**</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>-0.1773***</t>
+          <t>-0.2571**</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>-0.1999***</t>
+          <t>-0.2324**</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>-0.2020***</t>
+          <t>-0.2275**</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-0.1914***</t>
+          <t>-0.2261**</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>-0.2075***</t>
+          <t>-0.2300**</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-0.2314***</t>
+          <t>-0.2484***</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-0.2084***</t>
+          <t>-0.2234**</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-0.1891***</t>
+          <t>-0.2319**</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>-0.2104***</t>
+          <t>-0.2125**</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>-0.2447***</t>
+          <t>-0.2704**</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>-0.2607***</t>
+          <t>-0.2432**</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>-0.2614***</t>
+          <t>-0.2419**</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>-0.2422***</t>
+          <t>-0.2363**</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>-0.2619***</t>
+          <t>-0.2435**</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>-0.2663***</t>
+          <t>-0.2575**</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>-0.2623***</t>
+          <t>-0.2639**</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>-0.2422***</t>
+          <t>-0.2518**</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>-0.2698***</t>
+          <t>-0.2251**</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
         <is>
-          <t>-0.2498***</t>
+          <t>-0.2622**</t>
         </is>
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>-0.2501***</t>
+          <t>-0.2212**</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>-0.2489***</t>
+          <t>-0.2046*</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>-0.2430***</t>
+          <t>-0.2069**</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>-0.2378***</t>
+          <t>-0.1917*</t>
         </is>
       </c>
       <c r="AE105" s="2" t="inlineStr">
         <is>
-          <t>-0.2842***</t>
+          <t>-0.2467**</t>
         </is>
       </c>
       <c r="AF105" s="2" t="inlineStr">
         <is>
-          <t>-0.2441***</t>
+          <t>-0.2182**</t>
         </is>
       </c>
       <c r="AG105" s="2" t="inlineStr">
         <is>
-          <t>-0.2345***</t>
+          <t>-0.2294**</t>
         </is>
       </c>
       <c r="AH105" s="2" t="inlineStr">
         <is>
-          <t>-0.2375***</t>
+          <t>-0.2464***</t>
         </is>
       </c>
       <c r="AI105" s="2" t="inlineStr">
         <is>
-          <t>-0.2444***</t>
+          <t>-0.2505**</t>
         </is>
       </c>
       <c r="AJ105" s="2" t="inlineStr">
         <is>
-          <t>-0.2450***</t>
+          <t>-0.2074*</t>
         </is>
       </c>
       <c r="AK105" s="2" t="inlineStr">
         <is>
-          <t>-0.2444***</t>
+          <t>-0.1958*</t>
         </is>
       </c>
       <c r="AL105" s="2" t="inlineStr">
         <is>
-          <t>-0.2369***</t>
+          <t>-0.1951*</t>
         </is>
       </c>
       <c r="AM105" s="2" t="inlineStr">
         <is>
-          <t>-0.2346***</t>
+          <t>-0.1830*</t>
         </is>
       </c>
       <c r="AN105" s="2" t="inlineStr">
         <is>
-          <t>-0.2666***</t>
+          <t>-0.2136*</t>
         </is>
       </c>
       <c r="AO105" s="2" t="inlineStr">
         <is>
-          <t>-0.2401***</t>
+          <t>-0.2045*</t>
         </is>
       </c>
       <c r="AP105" s="2" t="inlineStr">
         <is>
-          <t>-0.2200***</t>
+          <t>-0.2001*</t>
         </is>
       </c>
       <c r="AQ105" s="2" t="inlineStr">
         <is>
-          <t>-0.2244***</t>
+          <t>-0.1935*</t>
         </is>
       </c>
     </row>
@@ -9070,429 +9070,429 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(0.0572)</t>
+          <t>(0.1120)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>(0.0547)</t>
+          <t>(0.1076)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>(0.0552)</t>
+          <t>(0.1025)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>(0.0556)</t>
+          <t>(0.1036)</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>(0.0530)</t>
+          <t>(0.0984)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>(0.0515)</t>
+          <t>(0.0951)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>(0.0622)</t>
+          <t>(0.1026)</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>(0.0652)</t>
+          <t>(0.0970)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>(0.0654)</t>
+          <t>(0.0998)</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>(0.0625)</t>
+          <t>(0.0959)</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>(0.0644)</t>
+          <t>(0.0927)</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>(0.0621)</t>
+          <t>(0.0935)</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>(0.0683)</t>
+          <t>(0.1058)</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>(0.0644)</t>
+          <t>(0.0926)</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>(0.0680)</t>
+          <t>(0.0904)</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>(0.0539)</t>
+          <t>(0.1131)</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>(0.0556)</t>
+          <t>(0.1082)</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>(0.0562)</t>
+          <t>(0.1095)</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>(0.0540)</t>
+          <t>(0.1041)</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>(0.0574)</t>
+          <t>(0.0990)</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>(0.0549)</t>
+          <t>(0.1074)</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>(0.0560)</t>
+          <t>(0.1198)</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>(0.0531)</t>
+          <t>(0.1086)</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>(0.0588)</t>
+          <t>(0.0975)</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
         <is>
-          <t>(0.0685)</t>
+          <t>(0.1109)</t>
         </is>
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>(0.0728)</t>
+          <t>(0.1060)</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>(0.0729)</t>
+          <t>(0.1105)</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>(0.0697)</t>
+          <t>(0.1055)</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>(0.0650)</t>
+          <t>(0.1013)</t>
         </is>
       </c>
       <c r="AE106" s="2" t="inlineStr">
         <is>
-          <t>(0.0729)</t>
+          <t>(0.1036)</t>
         </is>
       </c>
       <c r="AF106" s="2" t="inlineStr">
         <is>
-          <t>(0.0669)</t>
+          <t>(0.1062)</t>
         </is>
       </c>
       <c r="AG106" s="2" t="inlineStr">
         <is>
-          <t>(0.0593)</t>
+          <t>(0.0934)</t>
         </is>
       </c>
       <c r="AH106" s="2" t="inlineStr">
         <is>
-          <t>(0.0569)</t>
+          <t>(0.0792)</t>
         </is>
       </c>
       <c r="AI106" s="2" t="inlineStr">
         <is>
-          <t>(0.0638)</t>
+          <t>(0.1160)</t>
         </is>
       </c>
       <c r="AJ106" s="2" t="inlineStr">
         <is>
-          <t>(0.0662)</t>
+          <t>(0.1109)</t>
         </is>
       </c>
       <c r="AK106" s="2" t="inlineStr">
         <is>
-          <t>(0.0658)</t>
+          <t>(0.1148)</t>
         </is>
       </c>
       <c r="AL106" s="2" t="inlineStr">
         <is>
-          <t>(0.0627)</t>
+          <t>(0.1101)</t>
         </is>
       </c>
       <c r="AM106" s="2" t="inlineStr">
         <is>
-          <t>(0.0585)</t>
+          <t>(0.1025)</t>
         </is>
       </c>
       <c r="AN106" s="2" t="inlineStr">
         <is>
-          <t>(0.0669)</t>
+          <t>(0.1109)</t>
         </is>
       </c>
       <c r="AO106" s="2" t="inlineStr">
         <is>
-          <t>(0.0699)</t>
+          <t>(0.1127)</t>
         </is>
       </c>
       <c r="AP106" s="2" t="inlineStr">
         <is>
-          <t>(0.0595)</t>
+          <t>(0.1058)</t>
         </is>
       </c>
       <c r="AQ106" s="2" t="inlineStr">
         <is>
-          <t>(0.0641)</t>
+          <t>(0.0992)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Region FE: South Asia</t>
+          <t>Region FE: North America</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>-0.2547**</t>
+          <t>0.2444***</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>-0.2628**</t>
+          <t>0.2009***</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>-0.2375**</t>
+          <t>0.1059*</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>-0.2358**</t>
+          <t>0.1052</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-0.2271**</t>
+          <t>0.1135*</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>-0.2417**</t>
+          <t>0.0982*</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>-0.2571**</t>
+          <t>0.2269**</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>-0.2324**</t>
+          <t>0.1469</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>-0.2275**</t>
+          <t>0.1467</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>-0.2261**</t>
+          <t>0.1473*</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>-0.2300**</t>
+          <t>0.1414*</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>-0.2484***</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>-0.2234**</t>
+          <t>0.1944*</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>-0.2319**</t>
+          <t>0.2050**</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>-0.2125**</t>
+          <t>0.1496*</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>-0.2704**</t>
+          <t>0.1825***</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>-0.2432**</t>
+          <t>0.0945</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>-0.2419**</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>-0.2363**</t>
+          <t>0.0965</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
         <is>
-          <t>-0.2435**</t>
+          <t>0.0939</t>
         </is>
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>-0.2575**</t>
+          <t>0.1060</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>-0.2639**</t>
+          <t>0.1231*</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>-0.2518**</t>
+          <t>0.1171*</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>-0.2251**</t>
+          <t>0.0901</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
         <is>
-          <t>-0.2622**</t>
+          <t>0.2097***</t>
         </is>
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>-0.2212**</t>
+          <t>0.1248*</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>-0.2046*</t>
+          <t>0.1260*</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>-0.2069**</t>
+          <t>0.1288**</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>-0.1917*</t>
+          <t>0.1236**</t>
         </is>
       </c>
       <c r="AE107" s="2" t="inlineStr">
         <is>
-          <t>-0.2467**</t>
+          <t>0.1191*</t>
         </is>
       </c>
       <c r="AF107" s="2" t="inlineStr">
         <is>
-          <t>-0.2182**</t>
+          <t>0.1399**</t>
         </is>
       </c>
       <c r="AG107" s="2" t="inlineStr">
         <is>
-          <t>-0.2294**</t>
+          <t>0.1229**</t>
         </is>
       </c>
       <c r="AH107" s="2" t="inlineStr">
         <is>
-          <t>-0.2464***</t>
+          <t>0.1068*</t>
         </is>
       </c>
       <c r="AI107" s="2" t="inlineStr">
         <is>
-          <t>-0.2505**</t>
+          <t>0.2137***</t>
         </is>
       </c>
       <c r="AJ107" s="2" t="inlineStr">
         <is>
-          <t>-0.2074*</t>
+          <t>0.1262*</t>
         </is>
       </c>
       <c r="AK107" s="2" t="inlineStr">
         <is>
-          <t>-0.1958*</t>
+          <t>0.1267*</t>
         </is>
       </c>
       <c r="AL107" s="2" t="inlineStr">
         <is>
-          <t>-0.1951*</t>
+          <t>0.1304**</t>
         </is>
       </c>
       <c r="AM107" s="2" t="inlineStr">
         <is>
-          <t>-0.1830*</t>
+          <t>0.1235**</t>
         </is>
       </c>
       <c r="AN107" s="2" t="inlineStr">
         <is>
-          <t>-0.2136*</t>
+          <t>0.1286*</t>
         </is>
       </c>
       <c r="AO107" s="2" t="inlineStr">
         <is>
-          <t>-0.2045*</t>
+          <t>0.1265*</t>
         </is>
       </c>
       <c r="AP107" s="2" t="inlineStr">
         <is>
-          <t>-0.2001*</t>
+          <t>0.1230**</t>
         </is>
       </c>
       <c r="AQ107" s="2" t="inlineStr">
         <is>
-          <t>-0.1935*</t>
+          <t>0.1241**</t>
         </is>
       </c>
     </row>
@@ -9500,212 +9500,212 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>(0.1120)</t>
+          <t>(0.0540)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>(0.1076)</t>
+          <t>(0.0508)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>(0.1025)</t>
+          <t>(0.0641)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>(0.1036)</t>
+          <t>(0.0642)</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>(0.0984)</t>
+          <t>(0.0580)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
+          <t>(0.0552)</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>(0.0941)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>(0.0957)</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
           <t>(0.0951)</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>(0.1026)</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>(0.0970)</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>(0.0998)</t>
-        </is>
-      </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>(0.0959)</t>
+          <t>(0.0874)</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>(0.0927)</t>
+          <t>(0.0801)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>(0.0935)</t>
+          <t>(0.1023)</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>(0.1058)</t>
+          <t>(0.1056)</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>(0.0926)</t>
+          <t>(0.1001)</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>(0.0904)</t>
+          <t>(0.0807)</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>(0.1131)</t>
+          <t>(0.0637)</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>(0.1082)</t>
+          <t>(0.0704)</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>(0.1095)</t>
+          <t>(0.0705)</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>(0.1041)</t>
+          <t>(0.0646)</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>(0.0990)</t>
+          <t>(0.0584)</t>
         </is>
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>(0.1074)</t>
+          <t>(0.0692)</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>(0.1198)</t>
+          <t>(0.0713)</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>(0.1086)</t>
+          <t>(0.0678)</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>(0.0975)</t>
+          <t>(0.0616)</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
         <is>
-          <t>(0.1109)</t>
+          <t>(0.0628)</t>
         </is>
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>(0.1060)</t>
+          <t>(0.0692)</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>(0.1105)</t>
+          <t>(0.0685)</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>(0.1055)</t>
+          <t>(0.0618)</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>(0.1013)</t>
+          <t>(0.0581)</t>
         </is>
       </c>
       <c r="AE108" s="2" t="inlineStr">
         <is>
-          <t>(0.1036)</t>
+          <t>(0.0685)</t>
         </is>
       </c>
       <c r="AF108" s="2" t="inlineStr">
         <is>
-          <t>(0.1062)</t>
+          <t>(0.0629)</t>
         </is>
       </c>
       <c r="AG108" s="2" t="inlineStr">
         <is>
-          <t>(0.0934)</t>
+          <t>(0.0554)</t>
         </is>
       </c>
       <c r="AH108" s="2" t="inlineStr">
         <is>
-          <t>(0.0792)</t>
+          <t>(0.0547)</t>
         </is>
       </c>
       <c r="AI108" s="2" t="inlineStr">
         <is>
-          <t>(0.1160)</t>
+          <t>(0.0614)</t>
         </is>
       </c>
       <c r="AJ108" s="2" t="inlineStr">
         <is>
-          <t>(0.1109)</t>
+          <t>(0.0693)</t>
         </is>
       </c>
       <c r="AK108" s="2" t="inlineStr">
         <is>
-          <t>(0.1148)</t>
+          <t>(0.0689)</t>
         </is>
       </c>
       <c r="AL108" s="2" t="inlineStr">
         <is>
-          <t>(0.1101)</t>
+          <t>(0.0628)</t>
         </is>
       </c>
       <c r="AM108" s="2" t="inlineStr">
         <is>
-          <t>(0.1025)</t>
+          <t>(0.0583)</t>
         </is>
       </c>
       <c r="AN108" s="2" t="inlineStr">
         <is>
-          <t>(0.1109)</t>
+          <t>(0.0705)</t>
         </is>
       </c>
       <c r="AO108" s="2" t="inlineStr">
         <is>
-          <t>(0.1127)</t>
+          <t>(0.0696)</t>
         </is>
       </c>
       <c r="AP108" s="2" t="inlineStr">
         <is>
-          <t>(0.1058)</t>
+          <t>(0.0623)</t>
         </is>
       </c>
       <c r="AQ108" s="2" t="inlineStr">
         <is>
-          <t>(0.0992)</t>
+          <t>(0.0618)</t>
         </is>
       </c>
     </row>
@@ -15475,7 +15475,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_FLD_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
@@ -15509,7 +15509,7 @@
       <c r="AD57" s="2" t="inlineStr"/>
       <c r="AE57" s="2" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.0034</t>
         </is>
       </c>
       <c r="AF57" s="2" t="inlineStr"/>
@@ -15558,7 +15558,7 @@
       <c r="AD58" s="2" t="inlineStr"/>
       <c r="AE58" s="2" t="inlineStr">
         <is>
-          <t>(0.0015)</t>
+          <t>(0.0030)</t>
         </is>
       </c>
       <c r="AF58" s="2" t="inlineStr"/>
@@ -15577,7 +15577,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_3_HAZARDS_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
@@ -15609,7 +15609,11 @@
       <c r="AB59" s="2" t="inlineStr"/>
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr"/>
-      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr">
+        <is>
+          <t>0.0032**</t>
+        </is>
+      </c>
       <c r="AF59" s="2" t="inlineStr"/>
       <c r="AG59" s="2" t="inlineStr"/>
       <c r="AH59" s="2" t="inlineStr"/>
@@ -15618,11 +15622,7 @@
       <c r="AK59" s="2" t="inlineStr"/>
       <c r="AL59" s="2" t="inlineStr"/>
       <c r="AM59" s="2" t="inlineStr"/>
-      <c r="AN59" s="2" t="inlineStr">
-        <is>
-          <t>0.0014</t>
-        </is>
-      </c>
+      <c r="AN59" s="2" t="inlineStr"/>
       <c r="AO59" s="2" t="inlineStr"/>
       <c r="AP59" s="2" t="inlineStr"/>
       <c r="AQ59" s="2" t="inlineStr"/>
@@ -15658,7 +15658,11 @@
       <c r="AB60" s="2" t="inlineStr"/>
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr"/>
-      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr">
+        <is>
+          <t>(0.0014)</t>
+        </is>
+      </c>
       <c r="AF60" s="2" t="inlineStr"/>
       <c r="AG60" s="2" t="inlineStr"/>
       <c r="AH60" s="2" t="inlineStr"/>
@@ -15667,11 +15671,7 @@
       <c r="AK60" s="2" t="inlineStr"/>
       <c r="AL60" s="2" t="inlineStr"/>
       <c r="AM60" s="2" t="inlineStr"/>
-      <c r="AN60" s="2" t="inlineStr">
-        <is>
-          <t>(0.0011)</t>
-        </is>
-      </c>
+      <c r="AN60" s="2" t="inlineStr"/>
       <c r="AO60" s="2" t="inlineStr"/>
       <c r="AP60" s="2" t="inlineStr"/>
       <c r="AQ60" s="2" t="inlineStr"/>
@@ -15679,7 +15679,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_STM_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
@@ -15713,7 +15713,7 @@
       <c r="AD61" s="2" t="inlineStr"/>
       <c r="AE61" s="2" t="inlineStr">
         <is>
-          <t>0.0032**</t>
+          <t>0.0007</t>
         </is>
       </c>
       <c r="AF61" s="2" t="inlineStr"/>
@@ -15762,7 +15762,7 @@
       <c r="AD62" s="2" t="inlineStr"/>
       <c r="AE62" s="2" t="inlineStr">
         <is>
-          <t>(0.0014)</t>
+          <t>(0.0015)</t>
         </is>
       </c>
       <c r="AF62" s="2" t="inlineStr"/>
@@ -15781,7 +15781,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C_POVERTY:C_log_DIS_EQK_per_POP</t>
+          <t>C_POVERTY:C_log_DIS_3_HAZARDS_per_POP</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
@@ -15813,11 +15813,7 @@
       <c r="AB63" s="2" t="inlineStr"/>
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr"/>
-      <c r="AE63" s="2" t="inlineStr">
-        <is>
-          <t>-0.0034</t>
-        </is>
-      </c>
+      <c r="AE63" s="2" t="inlineStr"/>
       <c r="AF63" s="2" t="inlineStr"/>
       <c r="AG63" s="2" t="inlineStr"/>
       <c r="AH63" s="2" t="inlineStr"/>
@@ -15826,7 +15822,11 @@
       <c r="AK63" s="2" t="inlineStr"/>
       <c r="AL63" s="2" t="inlineStr"/>
       <c r="AM63" s="2" t="inlineStr"/>
-      <c r="AN63" s="2" t="inlineStr"/>
+      <c r="AN63" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
       <c r="AO63" s="2" t="inlineStr"/>
       <c r="AP63" s="2" t="inlineStr"/>
       <c r="AQ63" s="2" t="inlineStr"/>
@@ -15862,11 +15862,7 @@
       <c r="AB64" s="2" t="inlineStr"/>
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr"/>
-      <c r="AE64" s="2" t="inlineStr">
-        <is>
-          <t>(0.0030)</t>
-        </is>
-      </c>
+      <c r="AE64" s="2" t="inlineStr"/>
       <c r="AF64" s="2" t="inlineStr"/>
       <c r="AG64" s="2" t="inlineStr"/>
       <c r="AH64" s="2" t="inlineStr"/>
@@ -15875,7 +15871,11 @@
       <c r="AK64" s="2" t="inlineStr"/>
       <c r="AL64" s="2" t="inlineStr"/>
       <c r="AM64" s="2" t="inlineStr"/>
-      <c r="AN64" s="2" t="inlineStr"/>
+      <c r="AN64" s="2" t="inlineStr">
+        <is>
+          <t>(0.0011)</t>
+        </is>
+      </c>
       <c r="AO64" s="2" t="inlineStr"/>
       <c r="AP64" s="2" t="inlineStr"/>
       <c r="AQ64" s="2" t="inlineStr"/>
@@ -15883,7 +15883,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C_log_GDP:C_log_DIS_EQK_per_POP</t>
+          <t>C_log_GDP:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
@@ -15918,7 +15918,7 @@
       <c r="AE65" s="2" t="inlineStr"/>
       <c r="AF65" s="2" t="inlineStr">
         <is>
-          <t>0.0585***</t>
+          <t>-0.0489**</t>
         </is>
       </c>
       <c r="AG65" s="2" t="inlineStr"/>
@@ -15967,7 +15967,7 @@
       <c r="AE66" s="2" t="inlineStr"/>
       <c r="AF66" s="2" t="inlineStr">
         <is>
-          <t>(0.0191)</t>
+          <t>(0.0222)</t>
         </is>
       </c>
       <c r="AG66" s="2" t="inlineStr"/>
@@ -15985,7 +15985,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C_log_GDP:C_log_DIS_STM_per_POP</t>
+          <t>C_log_GDP:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
@@ -16020,7 +16020,7 @@
       <c r="AE67" s="2" t="inlineStr"/>
       <c r="AF67" s="2" t="inlineStr">
         <is>
-          <t>-0.0489**</t>
+          <t>-0.0183</t>
         </is>
       </c>
       <c r="AG67" s="2" t="inlineStr"/>
@@ -16069,7 +16069,7 @@
       <c r="AE68" s="2" t="inlineStr"/>
       <c r="AF68" s="2" t="inlineStr">
         <is>
-          <t>(0.0222)</t>
+          <t>(0.0237)</t>
         </is>
       </c>
       <c r="AG68" s="2" t="inlineStr"/>
@@ -16189,7 +16189,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C_log_GDP:C_log_DIS_FLD_per_POP</t>
+          <t>C_log_GDP:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
@@ -16224,7 +16224,7 @@
       <c r="AE71" s="2" t="inlineStr"/>
       <c r="AF71" s="2" t="inlineStr">
         <is>
-          <t>-0.0183</t>
+          <t>0.0585***</t>
         </is>
       </c>
       <c r="AG71" s="2" t="inlineStr"/>
@@ -16273,7 +16273,7 @@
       <c r="AE72" s="2" t="inlineStr"/>
       <c r="AF72" s="2" t="inlineStr">
         <is>
-          <t>(0.0237)</t>
+          <t>(0.0191)</t>
         </is>
       </c>
       <c r="AG72" s="2" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_FLD_per_POP</t>
+          <t>C_CWGI:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
@@ -16327,7 +16327,7 @@
       <c r="AF73" s="2" t="inlineStr"/>
       <c r="AG73" s="2" t="inlineStr">
         <is>
-          <t>-0.0202</t>
+          <t>-0.1065***</t>
         </is>
       </c>
       <c r="AH73" s="2" t="inlineStr"/>
@@ -16376,7 +16376,7 @@
       <c r="AF74" s="2" t="inlineStr"/>
       <c r="AG74" s="2" t="inlineStr">
         <is>
-          <t>(0.0268)</t>
+          <t>(0.0249)</t>
         </is>
       </c>
       <c r="AH74" s="2" t="inlineStr"/>
@@ -16393,7 +16393,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_EQK_per_POP</t>
+          <t>C_CWGI:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
@@ -16429,7 +16429,7 @@
       <c r="AF75" s="2" t="inlineStr"/>
       <c r="AG75" s="2" t="inlineStr">
         <is>
-          <t>0.0784***</t>
+          <t>-0.0202</t>
         </is>
       </c>
       <c r="AH75" s="2" t="inlineStr"/>
@@ -16478,7 +16478,7 @@
       <c r="AF76" s="2" t="inlineStr"/>
       <c r="AG76" s="2" t="inlineStr">
         <is>
-          <t>(0.0266)</t>
+          <t>(0.0268)</t>
         </is>
       </c>
       <c r="AH76" s="2" t="inlineStr"/>
@@ -16495,7 +16495,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_STM_per_POP</t>
+          <t>C_CWGI:C_log_DIS_3_HAZARDS_per_POP</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
@@ -16529,11 +16529,7 @@
       <c r="AD77" s="2" t="inlineStr"/>
       <c r="AE77" s="2" t="inlineStr"/>
       <c r="AF77" s="2" t="inlineStr"/>
-      <c r="AG77" s="2" t="inlineStr">
-        <is>
-          <t>-0.1065***</t>
-        </is>
-      </c>
+      <c r="AG77" s="2" t="inlineStr"/>
       <c r="AH77" s="2" t="inlineStr"/>
       <c r="AI77" s="2" t="inlineStr"/>
       <c r="AJ77" s="2" t="inlineStr"/>
@@ -16542,7 +16538,11 @@
       <c r="AM77" s="2" t="inlineStr"/>
       <c r="AN77" s="2" t="inlineStr"/>
       <c r="AO77" s="2" t="inlineStr"/>
-      <c r="AP77" s="2" t="inlineStr"/>
+      <c r="AP77" s="2" t="inlineStr">
+        <is>
+          <t>-0.0570**</t>
+        </is>
+      </c>
       <c r="AQ77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
@@ -16578,11 +16578,7 @@
       <c r="AD78" s="2" t="inlineStr"/>
       <c r="AE78" s="2" t="inlineStr"/>
       <c r="AF78" s="2" t="inlineStr"/>
-      <c r="AG78" s="2" t="inlineStr">
-        <is>
-          <t>(0.0249)</t>
-        </is>
-      </c>
+      <c r="AG78" s="2" t="inlineStr"/>
       <c r="AH78" s="2" t="inlineStr"/>
       <c r="AI78" s="2" t="inlineStr"/>
       <c r="AJ78" s="2" t="inlineStr"/>
@@ -16591,13 +16587,17 @@
       <c r="AM78" s="2" t="inlineStr"/>
       <c r="AN78" s="2" t="inlineStr"/>
       <c r="AO78" s="2" t="inlineStr"/>
-      <c r="AP78" s="2" t="inlineStr"/>
+      <c r="AP78" s="2" t="inlineStr">
+        <is>
+          <t>(0.0256)</t>
+        </is>
+      </c>
       <c r="AQ78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C_CWGI:C_log_DIS_3_HAZARDS_per_POP</t>
+          <t>C_CWGI:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
@@ -16631,7 +16631,11 @@
       <c r="AD79" s="2" t="inlineStr"/>
       <c r="AE79" s="2" t="inlineStr"/>
       <c r="AF79" s="2" t="inlineStr"/>
-      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr">
+        <is>
+          <t>0.0784***</t>
+        </is>
+      </c>
       <c r="AH79" s="2" t="inlineStr"/>
       <c r="AI79" s="2" t="inlineStr"/>
       <c r="AJ79" s="2" t="inlineStr"/>
@@ -16640,11 +16644,7 @@
       <c r="AM79" s="2" t="inlineStr"/>
       <c r="AN79" s="2" t="inlineStr"/>
       <c r="AO79" s="2" t="inlineStr"/>
-      <c r="AP79" s="2" t="inlineStr">
-        <is>
-          <t>-0.0570**</t>
-        </is>
-      </c>
+      <c r="AP79" s="2" t="inlineStr"/>
       <c r="AQ79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
@@ -16680,7 +16680,11 @@
       <c r="AD80" s="2" t="inlineStr"/>
       <c r="AE80" s="2" t="inlineStr"/>
       <c r="AF80" s="2" t="inlineStr"/>
-      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr">
+        <is>
+          <t>(0.0266)</t>
+        </is>
+      </c>
       <c r="AH80" s="2" t="inlineStr"/>
       <c r="AI80" s="2" t="inlineStr"/>
       <c r="AJ80" s="2" t="inlineStr"/>
@@ -16689,17 +16693,13 @@
       <c r="AM80" s="2" t="inlineStr"/>
       <c r="AN80" s="2" t="inlineStr"/>
       <c r="AO80" s="2" t="inlineStr"/>
-      <c r="AP80" s="2" t="inlineStr">
-        <is>
-          <t>(0.0256)</t>
-        </is>
-      </c>
+      <c r="AP80" s="2" t="inlineStr"/>
       <c r="AQ80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C_CDBQ:C_log_DIS_STM_per_POP</t>
+          <t>C_CDBQ:C_log_DIS_FLD_per_POP</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
@@ -16736,7 +16736,7 @@
       <c r="AG81" s="2" t="inlineStr"/>
       <c r="AH81" s="2" t="inlineStr">
         <is>
-          <t>-0.0084*</t>
+          <t>0.0021</t>
         </is>
       </c>
       <c r="AI81" s="2" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       <c r="AG82" s="2" t="inlineStr"/>
       <c r="AH82" s="2" t="inlineStr">
         <is>
-          <t>(0.0049)</t>
+          <t>(0.0060)</t>
         </is>
       </c>
       <c r="AI82" s="2" t="inlineStr"/>
@@ -16801,7 +16801,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C_CDBQ:C_log_DIS_EQK_per_POP</t>
+          <t>C_CDBQ:C_log_DIS_STM_per_POP</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       <c r="AG83" s="2" t="inlineStr"/>
       <c r="AH83" s="2" t="inlineStr">
         <is>
-          <t>0.0240*</t>
+          <t>-0.0084*</t>
         </is>
       </c>
       <c r="AI83" s="2" t="inlineStr"/>
@@ -16887,7 +16887,7 @@
       <c r="AG84" s="2" t="inlineStr"/>
       <c r="AH84" s="2" t="inlineStr">
         <is>
-          <t>(0.0123)</t>
+          <t>(0.0049)</t>
         </is>
       </c>
       <c r="AI84" s="2" t="inlineStr"/>
@@ -16903,7 +16903,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C_CDBQ:C_log_DIS_FLD_per_POP</t>
+          <t>C_CDBQ:C_log_DIS_EQK_per_POP</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
@@ -16940,7 +16940,7 @@
       <c r="AG85" s="2" t="inlineStr"/>
       <c r="AH85" s="2" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0240*</t>
         </is>
       </c>
       <c r="AI85" s="2" t="inlineStr"/>
@@ -16989,7 +16989,7 @@
       <c r="AG86" s="2" t="inlineStr"/>
       <c r="AH86" s="2" t="inlineStr">
         <is>
-          <t>(0.0060)</t>
+          <t>(0.0123)</t>
         </is>
       </c>
       <c r="AI86" s="2" t="inlineStr"/>
@@ -17107,7 +17107,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Earthquake Count (per Pop)</t>
+          <t>Storm Count (per Pop)</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
@@ -17136,47 +17136,47 @@
       <c r="Y89" s="2" t="inlineStr"/>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>0.0641*</t>
+          <t>-0.0595***</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>0.0700*</t>
+          <t>-0.0561***</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>0.0803**</t>
+          <t>-0.0498**</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>0.0798**</t>
+          <t>-0.0544**</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>0.0792**</t>
+          <t>-0.0522**</t>
         </is>
       </c>
       <c r="AE89" s="2" t="inlineStr">
         <is>
-          <t>0.0574**</t>
+          <t>-0.0477***</t>
         </is>
       </c>
       <c r="AF89" s="2" t="inlineStr">
         <is>
-          <t>0.0707**</t>
+          <t>-0.0672***</t>
         </is>
       </c>
       <c r="AG89" s="2" t="inlineStr">
         <is>
-          <t>0.0315</t>
+          <t>-0.0460***</t>
         </is>
       </c>
       <c r="AH89" s="2" t="inlineStr">
         <is>
-          <t>0.1319**</t>
+          <t>-0.0786***</t>
         </is>
       </c>
       <c r="AI89" s="2" t="inlineStr"/>
@@ -17217,47 +17217,47 @@
       <c r="Y90" s="2" t="inlineStr"/>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>(0.0381)</t>
+          <t>(0.0203)</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>(0.0360)</t>
+          <t>(0.0201)</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>(0.0359)</t>
+          <t>(0.0214)</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>(0.0353)</t>
+          <t>(0.0220)</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>(0.0361)</t>
+          <t>(0.0252)</t>
         </is>
       </c>
       <c r="AE90" s="2" t="inlineStr">
         <is>
-          <t>(0.0287)</t>
+          <t>(0.0176)</t>
         </is>
       </c>
       <c r="AF90" s="2" t="inlineStr">
         <is>
-          <t>(0.0305)</t>
+          <t>(0.0206)</t>
         </is>
       </c>
       <c r="AG90" s="2" t="inlineStr">
         <is>
-          <t>(0.0291)</t>
+          <t>(0.0171)</t>
         </is>
       </c>
       <c r="AH90" s="2" t="inlineStr">
         <is>
-          <t>(0.0553)</t>
+          <t>(0.0288)</t>
         </is>
       </c>
       <c r="AI90" s="2" t="inlineStr"/>
@@ -17273,7 +17273,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Flood Count (per Pop)</t>
+          <t>3 Hazards (per Pop)</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
@@ -17300,60 +17300,60 @@
       <c r="W91" s="2" t="inlineStr"/>
       <c r="X91" s="2" t="inlineStr"/>
       <c r="Y91" s="2" t="inlineStr"/>
-      <c r="Z91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0609***</t>
-        </is>
-      </c>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0489**</t>
-        </is>
-      </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0498**</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0478**</t>
-        </is>
-      </c>
-      <c r="AD91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0466**</t>
-        </is>
-      </c>
-      <c r="AE91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0490**</t>
-        </is>
-      </c>
-      <c r="AF91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0618***</t>
-        </is>
-      </c>
-      <c r="AG91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0474**</t>
-        </is>
-      </c>
-      <c r="AH91" s="2" t="inlineStr">
-        <is>
-          <t>-0.0605**</t>
-        </is>
-      </c>
-      <c r="AI91" s="2" t="inlineStr"/>
-      <c r="AJ91" s="2" t="inlineStr"/>
-      <c r="AK91" s="2" t="inlineStr"/>
-      <c r="AL91" s="2" t="inlineStr"/>
-      <c r="AM91" s="2" t="inlineStr"/>
-      <c r="AN91" s="2" t="inlineStr"/>
-      <c r="AO91" s="2" t="inlineStr"/>
-      <c r="AP91" s="2" t="inlineStr"/>
-      <c r="AQ91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0596***</t>
+        </is>
+      </c>
+      <c r="AJ91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0479***</t>
+        </is>
+      </c>
+      <c r="AK91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0423**</t>
+        </is>
+      </c>
+      <c r="AL91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0450**</t>
+        </is>
+      </c>
+      <c r="AM91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0369</t>
+        </is>
+      </c>
+      <c r="AN91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0438***</t>
+        </is>
+      </c>
+      <c r="AO91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0513***</t>
+        </is>
+      </c>
+      <c r="AP91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0461***</t>
+        </is>
+      </c>
+      <c r="AQ91" s="2" t="inlineStr">
+        <is>
+          <t>-0.0417*</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -17381,65 +17381,65 @@
       <c r="W92" s="2" t="inlineStr"/>
       <c r="X92" s="2" t="inlineStr"/>
       <c r="Y92" s="2" t="inlineStr"/>
-      <c r="Z92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0214)</t>
-        </is>
-      </c>
-      <c r="AA92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0207)</t>
-        </is>
-      </c>
-      <c r="AB92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0212)</t>
-        </is>
-      </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0212)</t>
-        </is>
-      </c>
-      <c r="AD92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0220)</t>
-        </is>
-      </c>
-      <c r="AE92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0202)</t>
-        </is>
-      </c>
-      <c r="AF92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0205)</t>
-        </is>
-      </c>
-      <c r="AG92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0192)</t>
-        </is>
-      </c>
-      <c r="AH92" s="2" t="inlineStr">
-        <is>
-          <t>(0.0269)</t>
-        </is>
-      </c>
-      <c r="AI92" s="2" t="inlineStr"/>
-      <c r="AJ92" s="2" t="inlineStr"/>
-      <c r="AK92" s="2" t="inlineStr"/>
-      <c r="AL92" s="2" t="inlineStr"/>
-      <c r="AM92" s="2" t="inlineStr"/>
-      <c r="AN92" s="2" t="inlineStr"/>
-      <c r="AO92" s="2" t="inlineStr"/>
-      <c r="AP92" s="2" t="inlineStr"/>
-      <c r="AQ92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0168)</t>
+        </is>
+      </c>
+      <c r="AJ92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0166)</t>
+        </is>
+      </c>
+      <c r="AK92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0195)</t>
+        </is>
+      </c>
+      <c r="AL92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0197)</t>
+        </is>
+      </c>
+      <c r="AM92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0229)</t>
+        </is>
+      </c>
+      <c r="AN92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0157)</t>
+        </is>
+      </c>
+      <c r="AO92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0184)</t>
+        </is>
+      </c>
+      <c r="AP92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0156)</t>
+        </is>
+      </c>
+      <c r="AQ92" s="2" t="inlineStr">
+        <is>
+          <t>(0.0217)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Storm Count (per Pop)</t>
+          <t>Flood Count (per Pop)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
@@ -17468,12 +17468,12 @@
       <c r="Y93" s="2" t="inlineStr"/>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>-0.0595***</t>
+          <t>-0.0609***</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>-0.0561***</t>
+          <t>-0.0489**</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -17483,32 +17483,32 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>-0.0544**</t>
+          <t>-0.0478**</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>-0.0522**</t>
+          <t>-0.0466**</t>
         </is>
       </c>
       <c r="AE93" s="2" t="inlineStr">
         <is>
-          <t>-0.0477***</t>
+          <t>-0.0490**</t>
         </is>
       </c>
       <c r="AF93" s="2" t="inlineStr">
         <is>
-          <t>-0.0672***</t>
+          <t>-0.0618***</t>
         </is>
       </c>
       <c r="AG93" s="2" t="inlineStr">
         <is>
-          <t>-0.0460***</t>
+          <t>-0.0474**</t>
         </is>
       </c>
       <c r="AH93" s="2" t="inlineStr">
         <is>
-          <t>-0.0786***</t>
+          <t>-0.0605**</t>
         </is>
       </c>
       <c r="AI93" s="2" t="inlineStr"/>
@@ -17549,47 +17549,47 @@
       <c r="Y94" s="2" t="inlineStr"/>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>(0.0203)</t>
+          <t>(0.0214)</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>(0.0201)</t>
+          <t>(0.0207)</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>(0.0214)</t>
+          <t>(0.0212)</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
+          <t>(0.0212)</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
           <t>(0.0220)</t>
         </is>
       </c>
-      <c r="AD94" s="2" t="inlineStr">
-        <is>
-          <t>(0.0252)</t>
-        </is>
-      </c>
       <c r="AE94" s="2" t="inlineStr">
         <is>
-          <t>(0.0176)</t>
+          <t>(0.0202)</t>
         </is>
       </c>
       <c r="AF94" s="2" t="inlineStr">
         <is>
-          <t>(0.0206)</t>
+          <t>(0.0205)</t>
         </is>
       </c>
       <c r="AG94" s="2" t="inlineStr">
         <is>
-          <t>(0.0171)</t>
+          <t>(0.0192)</t>
         </is>
       </c>
       <c r="AH94" s="2" t="inlineStr">
         <is>
-          <t>(0.0288)</t>
+          <t>(0.0269)</t>
         </is>
       </c>
       <c r="AI94" s="2" t="inlineStr"/>
@@ -17605,7 +17605,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3 Hazards (per Pop)</t>
+          <t>Earthquake Count (per Pop)</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr"/>
@@ -17632,60 +17632,60 @@
       <c r="W95" s="2" t="inlineStr"/>
       <c r="X95" s="2" t="inlineStr"/>
       <c r="Y95" s="2" t="inlineStr"/>
-      <c r="Z95" s="2" t="inlineStr"/>
-      <c r="AA95" s="2" t="inlineStr"/>
-      <c r="AB95" s="2" t="inlineStr"/>
-      <c r="AC95" s="2" t="inlineStr"/>
-      <c r="AD95" s="2" t="inlineStr"/>
-      <c r="AE95" s="2" t="inlineStr"/>
-      <c r="AF95" s="2" t="inlineStr"/>
-      <c r="AG95" s="2" t="inlineStr"/>
-      <c r="AH95" s="2" t="inlineStr"/>
-      <c r="AI95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0596***</t>
-        </is>
-      </c>
-      <c r="AJ95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0479***</t>
-        </is>
-      </c>
-      <c r="AK95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0423**</t>
-        </is>
-      </c>
-      <c r="AL95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0450**</t>
-        </is>
-      </c>
-      <c r="AM95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0369</t>
-        </is>
-      </c>
-      <c r="AN95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0438***</t>
-        </is>
-      </c>
-      <c r="AO95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0513***</t>
-        </is>
-      </c>
-      <c r="AP95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0461***</t>
-        </is>
-      </c>
-      <c r="AQ95" s="2" t="inlineStr">
-        <is>
-          <t>-0.0417*</t>
-        </is>
-      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>0.0641*</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0.0700*</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0.0803**</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>0.0798**</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>0.0792**</t>
+        </is>
+      </c>
+      <c r="AE95" s="2" t="inlineStr">
+        <is>
+          <t>0.0574**</t>
+        </is>
+      </c>
+      <c r="AF95" s="2" t="inlineStr">
+        <is>
+          <t>0.0707**</t>
+        </is>
+      </c>
+      <c r="AG95" s="2" t="inlineStr">
+        <is>
+          <t>0.0315</t>
+        </is>
+      </c>
+      <c r="AH95" s="2" t="inlineStr">
+        <is>
+          <t>0.1319**</t>
+        </is>
+      </c>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+      <c r="AK95" s="2" t="inlineStr"/>
+      <c r="AL95" s="2" t="inlineStr"/>
+      <c r="AM95" s="2" t="inlineStr"/>
+      <c r="AN95" s="2" t="inlineStr"/>
+      <c r="AO95" s="2" t="inlineStr"/>
+      <c r="AP95" s="2" t="inlineStr"/>
+      <c r="AQ95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -17713,275 +17713,275 @@
       <c r="W96" s="2" t="inlineStr"/>
       <c r="X96" s="2" t="inlineStr"/>
       <c r="Y96" s="2" t="inlineStr"/>
-      <c r="Z96" s="2" t="inlineStr"/>
-      <c r="AA96" s="2" t="inlineStr"/>
-      <c r="AB96" s="2" t="inlineStr"/>
-      <c r="AC96" s="2" t="inlineStr"/>
-      <c r="AD96" s="2" t="inlineStr"/>
-      <c r="AE96" s="2" t="inlineStr"/>
-      <c r="AF96" s="2" t="inlineStr"/>
-      <c r="AG96" s="2" t="inlineStr"/>
-      <c r="AH96" s="2" t="inlineStr"/>
-      <c r="AI96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0168)</t>
-        </is>
-      </c>
-      <c r="AJ96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0166)</t>
-        </is>
-      </c>
-      <c r="AK96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0195)</t>
-        </is>
-      </c>
-      <c r="AL96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0197)</t>
-        </is>
-      </c>
-      <c r="AM96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0229)</t>
-        </is>
-      </c>
-      <c r="AN96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0157)</t>
-        </is>
-      </c>
-      <c r="AO96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0184)</t>
-        </is>
-      </c>
-      <c r="AP96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0156)</t>
-        </is>
-      </c>
-      <c r="AQ96" s="2" t="inlineStr">
-        <is>
-          <t>(0.0217)</t>
-        </is>
-      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0381)</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0360)</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0359)</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0353)</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0361)</t>
+        </is>
+      </c>
+      <c r="AE96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0287)</t>
+        </is>
+      </c>
+      <c r="AF96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0305)</t>
+        </is>
+      </c>
+      <c r="AG96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0291)</t>
+        </is>
+      </c>
+      <c r="AH96" s="2" t="inlineStr">
+        <is>
+          <t>(0.0553)</t>
+        </is>
+      </c>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+      <c r="AK96" s="2" t="inlineStr"/>
+      <c r="AL96" s="2" t="inlineStr"/>
+      <c r="AM96" s="2" t="inlineStr"/>
+      <c r="AN96" s="2" t="inlineStr"/>
+      <c r="AO96" s="2" t="inlineStr"/>
+      <c r="AP96" s="2" t="inlineStr"/>
+      <c r="AQ96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Region FE: Middle East &amp; North Africa</t>
+          <t>Region FE: Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>0.2753***</t>
+          <t>0.2094***</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>0.2544***</t>
+          <t>0.1781***</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>0.2413***</t>
+          <t>0.1085</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>0.2082**</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>0.2191**</t>
+          <t>0.1183*</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>0.1933**</t>
+          <t>0.1110</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0.2788***</t>
+          <t>0.2020***</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>0.2500***</t>
+          <t>0.1213*</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>0.2107**</t>
+          <t>0.1213*</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0.2207**</t>
+          <t>0.1283*</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>0.1818**</t>
+          <t>0.1110</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0.2365**</t>
+          <t>0.1112</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>0.2268**</t>
+          <t>0.1123*</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>0.2656***</t>
+          <t>0.1316*</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0.1980**</t>
+          <t>0.0957</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>0.2636***</t>
+          <t>0.1844***</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>0.2455***</t>
+          <t>0.1117*</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>0.2098**</t>
+          <t>0.1116*</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>0.2233**</t>
+          <t>0.1212*</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>0.1730**</t>
+          <t>0.0987</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0.2377***</t>
+          <t>0.1039</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>0.2330***</t>
+          <t>0.1035</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>0.2445***</t>
+          <t>0.1090*</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>0.1994**</t>
+          <t>0.0890</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>0.1460</t>
+          <t>0.0939</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>0.1524*</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>0.1370</t>
+          <t>0.0587</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>0.1514*</t>
+          <t>0.0672</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>0.1503*</t>
+          <t>0.0685</t>
         </is>
       </c>
       <c r="AE97" s="2" t="inlineStr">
         <is>
-          <t>0.1403</t>
+          <t>0.0398</t>
         </is>
       </c>
       <c r="AF97" s="2" t="inlineStr">
         <is>
-          <t>0.1479*</t>
+          <t>0.0549</t>
         </is>
       </c>
       <c r="AG97" s="2" t="inlineStr">
         <is>
-          <t>0.1469*</t>
+          <t>0.0474</t>
         </is>
       </c>
       <c r="AH97" s="2" t="inlineStr">
         <is>
-          <t>0.1430</t>
+          <t>0.0330</t>
         </is>
       </c>
       <c r="AI97" s="2" t="inlineStr">
         <is>
-          <t>0.1611*</t>
+          <t>0.1142*</t>
         </is>
       </c>
       <c r="AJ97" s="2" t="inlineStr">
         <is>
-          <t>0.1683*</t>
+          <t>0.0679</t>
         </is>
       </c>
       <c r="AK97" s="2" t="inlineStr">
         <is>
-          <t>0.1582*</t>
+          <t>0.0738</t>
         </is>
       </c>
       <c r="AL97" s="2" t="inlineStr">
         <is>
-          <t>0.1726*</t>
+          <t>0.0841</t>
         </is>
       </c>
       <c r="AM97" s="2" t="inlineStr">
         <is>
-          <t>0.1684*</t>
+          <t>0.0867</t>
         </is>
       </c>
       <c r="AN97" s="2" t="inlineStr">
         <is>
-          <t>0.1654*</t>
+          <t>0.0675</t>
         </is>
       </c>
       <c r="AO97" s="2" t="inlineStr">
         <is>
-          <t>0.1723*</t>
+          <t>0.0749</t>
         </is>
       </c>
       <c r="AP97" s="2" t="inlineStr">
         <is>
-          <t>0.1766**</t>
+          <t>0.0732</t>
         </is>
       </c>
       <c r="AQ97" s="2" t="inlineStr">
         <is>
-          <t>0.1669*</t>
+          <t>0.0683</t>
         </is>
       </c>
     </row>
@@ -17989,212 +17989,212 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>(0.0919)</t>
+          <t>(0.0630)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>(0.0899)</t>
+          <t>(0.0657)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>(0.0874)</t>
+          <t>(0.0675)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>(0.0878)</t>
+          <t>(0.0675)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>(0.0912)</t>
+          <t>(0.0686)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>(0.0910)</t>
+          <t>(0.0679)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>(0.0911)</t>
+          <t>(0.0655)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>(0.0906)</t>
+          <t>(0.0681)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>(0.0898)</t>
+          <t>(0.0683)</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>(0.0926)</t>
+          <t>(0.0682)</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>(0.0908)</t>
+          <t>(0.0683)</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>(0.0938)</t>
+          <t>(0.0702)</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>(0.0912)</t>
+          <t>(0.0664)</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>(0.0953)</t>
+          <t>(0.0678)</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>(0.0961)</t>
+          <t>(0.0737)</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>(0.0876)</t>
+          <t>(0.0630)</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>(0.0853)</t>
+          <t>(0.0659)</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>(0.0865)</t>
+          <t>(0.0663)</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>(0.0892)</t>
+          <t>(0.0660)</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>(0.0879)</t>
+          <t>(0.0662)</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>(0.0850)</t>
+          <t>(0.0665)</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>(0.0866)</t>
+          <t>(0.0658)</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>(0.0899)</t>
+          <t>(0.0654)</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>(0.0896)</t>
+          <t>(0.0707)</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>(0.0908)</t>
+          <t>(0.0631)</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>(0.0901)</t>
+          <t>(0.0672)</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>(0.0886)</t>
+          <t>(0.0693)</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>(0.0906)</t>
+          <t>(0.0692)</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>(0.0909)</t>
+          <t>(0.0694)</t>
         </is>
       </c>
       <c r="AE98" s="2" t="inlineStr">
         <is>
-          <t>(0.0905)</t>
+          <t>(0.0670)</t>
         </is>
       </c>
       <c r="AF98" s="2" t="inlineStr">
         <is>
-          <t>(0.0876)</t>
+          <t>(0.0643)</t>
         </is>
       </c>
       <c r="AG98" s="2" t="inlineStr">
         <is>
-          <t>(0.0859)</t>
+          <t>(0.0595)</t>
         </is>
       </c>
       <c r="AH98" s="2" t="inlineStr">
         <is>
-          <t>(0.0905)</t>
+          <t>(0.0703)</t>
         </is>
       </c>
       <c r="AI98" s="2" t="inlineStr">
         <is>
-          <t>(0.0913)</t>
+          <t>(0.0637)</t>
         </is>
       </c>
       <c r="AJ98" s="2" t="inlineStr">
         <is>
-          <t>(0.0908)</t>
+          <t>(0.0669)</t>
         </is>
       </c>
       <c r="AK98" s="2" t="inlineStr">
         <is>
-          <t>(0.0897)</t>
+          <t>(0.0685)</t>
         </is>
       </c>
       <c r="AL98" s="2" t="inlineStr">
         <is>
-          <t>(0.0919)</t>
+          <t>(0.0689)</t>
         </is>
       </c>
       <c r="AM98" s="2" t="inlineStr">
         <is>
-          <t>(0.0922)</t>
+          <t>(0.0690)</t>
         </is>
       </c>
       <c r="AN98" s="2" t="inlineStr">
         <is>
-          <t>(0.0907)</t>
+          <t>(0.0666)</t>
         </is>
       </c>
       <c r="AO98" s="2" t="inlineStr">
         <is>
-          <t>(0.0903)</t>
+          <t>(0.0672)</t>
         </is>
       </c>
       <c r="AP98" s="2" t="inlineStr">
         <is>
-          <t>(0.0894)</t>
+          <t>(0.0643)</t>
         </is>
       </c>
       <c r="AQ98" s="2" t="inlineStr">
         <is>
-          <t>(0.0917)</t>
+          <t>(0.0687)</t>
         </is>
       </c>
     </row>
@@ -18631,217 +18631,217 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Region FE: Europe &amp; Central Asia</t>
+          <t>Region FE: Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>0.2094***</t>
+          <t>-0.0672</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>0.1781***</t>
+          <t>-0.0249</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>0.1085</t>
+          <t>-0.0408</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>-0.0495</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>0.1183*</t>
+          <t>-0.0453</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>0.1110</t>
+          <t>-0.0587</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0.2020***</t>
+          <t>0.0209</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>0.1213*</t>
+          <t>-0.0069</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>0.1213*</t>
+          <t>-0.0172</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0.1283*</t>
+          <t>-0.0139</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>0.1110</t>
+          <t>-0.0376</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0.1112</t>
+          <t>-0.0312</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>0.1123*</t>
+          <t>-0.0530</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0.1316*</t>
+          <t>-0.0117</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>0.0957</t>
+          <t>-0.0397</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>0.1844***</t>
+          <t>-0.0178</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>0.1117*</t>
+          <t>-0.0374</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>0.1116*</t>
+          <t>-0.0484</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>0.1212*</t>
+          <t>-0.0424</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>0.0987</t>
+          <t>-0.0718</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>0.1039</t>
+          <t>-0.0419</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>0.1035</t>
+          <t>-0.0400</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>0.1090*</t>
+          <t>-0.0323</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>0.0890</t>
+          <t>-0.0642</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
-          <t>0.0939</t>
+          <t>-0.1066**</t>
         </is>
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>-0.1069*</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>0.0587</t>
+          <t>-0.1049*</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>0.0672</t>
+          <t>-0.1013*</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>0.0685</t>
+          <t>-0.1008*</t>
         </is>
       </c>
       <c r="AE101" s="2" t="inlineStr">
         <is>
-          <t>0.0398</t>
+          <t>-0.0880</t>
         </is>
       </c>
       <c r="AF101" s="2" t="inlineStr">
         <is>
-          <t>0.0549</t>
+          <t>-0.0644</t>
         </is>
       </c>
       <c r="AG101" s="2" t="inlineStr">
         <is>
-          <t>0.0474</t>
+          <t>-0.0720</t>
         </is>
       </c>
       <c r="AH101" s="2" t="inlineStr">
         <is>
-          <t>0.0330</t>
+          <t>-0.0983*</t>
         </is>
       </c>
       <c r="AI101" s="2" t="inlineStr">
         <is>
-          <t>0.1142*</t>
+          <t>-0.0904*</t>
         </is>
       </c>
       <c r="AJ101" s="2" t="inlineStr">
         <is>
-          <t>0.0679</t>
+          <t>-0.0910*</t>
         </is>
       </c>
       <c r="AK101" s="2" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>-0.0901*</t>
         </is>
       </c>
       <c r="AL101" s="2" t="inlineStr">
         <is>
-          <t>0.0841</t>
+          <t>-0.0857</t>
         </is>
       </c>
       <c r="AM101" s="2" t="inlineStr">
         <is>
-          <t>0.0867</t>
+          <t>-0.0849</t>
         </is>
       </c>
       <c r="AN101" s="2" t="inlineStr">
         <is>
-          <t>0.0675</t>
+          <t>-0.0739</t>
         </is>
       </c>
       <c r="AO101" s="2" t="inlineStr">
         <is>
-          <t>0.0749</t>
+          <t>-0.0668</t>
         </is>
       </c>
       <c r="AP101" s="2" t="inlineStr">
         <is>
-          <t>0.0732</t>
+          <t>-0.0487</t>
         </is>
       </c>
       <c r="AQ101" s="2" t="inlineStr">
         <is>
-          <t>0.0683</t>
+          <t>-0.0916*</t>
         </is>
       </c>
     </row>
@@ -18849,429 +18849,429 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>(0.0630)</t>
+          <t>(0.0546)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>(0.0657)</t>
+          <t>(0.0542)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>(0.0675)</t>
+          <t>(0.0543)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>(0.0675)</t>
+          <t>(0.0538)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>(0.0686)</t>
+          <t>(0.0545)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>(0.0679)</t>
+          <t>(0.0526)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>(0.0655)</t>
+          <t>(0.0613)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>(0.0681)</t>
+          <t>(0.0628)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>(0.0683)</t>
+          <t>(0.0629)</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>(0.0682)</t>
+          <t>(0.0627)</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>(0.0683)</t>
+          <t>(0.0631)</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>(0.0702)</t>
+          <t>(0.0614)</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>(0.0664)</t>
+          <t>(0.0638)</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>(0.0678)</t>
+          <t>(0.0602)</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>(0.0737)</t>
+          <t>(0.0615)</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>(0.0630)</t>
+          <t>(0.0532)</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>(0.0659)</t>
+          <t>(0.0534)</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>(0.0663)</t>
+          <t>(0.0543)</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>(0.0660)</t>
+          <t>(0.0543)</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>(0.0662)</t>
+          <t>(0.0551)</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>(0.0665)</t>
+          <t>(0.0516)</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>(0.0658)</t>
+          <t>(0.0514)</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>(0.0654)</t>
+          <t>(0.0522)</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>(0.0707)</t>
+          <t>(0.0544)</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>(0.0631)</t>
+          <t>(0.0534)</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>(0.0672)</t>
+          <t>(0.0552)</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>(0.0693)</t>
+          <t>(0.0549)</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>(0.0692)</t>
+          <t>(0.0546)</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>(0.0694)</t>
+          <t>(0.0543)</t>
         </is>
       </c>
       <c r="AE102" s="2" t="inlineStr">
         <is>
-          <t>(0.0670)</t>
+          <t>(0.0572)</t>
         </is>
       </c>
       <c r="AF102" s="2" t="inlineStr">
         <is>
-          <t>(0.0643)</t>
+          <t>(0.0614)</t>
         </is>
       </c>
       <c r="AG102" s="2" t="inlineStr">
         <is>
-          <t>(0.0595)</t>
+          <t>(0.0515)</t>
         </is>
       </c>
       <c r="AH102" s="2" t="inlineStr">
         <is>
-          <t>(0.0703)</t>
+          <t>(0.0526)</t>
         </is>
       </c>
       <c r="AI102" s="2" t="inlineStr">
         <is>
-          <t>(0.0637)</t>
+          <t>(0.0529)</t>
         </is>
       </c>
       <c r="AJ102" s="2" t="inlineStr">
         <is>
-          <t>(0.0669)</t>
+          <t>(0.0531)</t>
         </is>
       </c>
       <c r="AK102" s="2" t="inlineStr">
         <is>
-          <t>(0.0685)</t>
+          <t>(0.0529)</t>
         </is>
       </c>
       <c r="AL102" s="2" t="inlineStr">
         <is>
-          <t>(0.0689)</t>
+          <t>(0.0530)</t>
         </is>
       </c>
       <c r="AM102" s="2" t="inlineStr">
         <is>
-          <t>(0.0690)</t>
+          <t>(0.0523)</t>
         </is>
       </c>
       <c r="AN102" s="2" t="inlineStr">
         <is>
-          <t>(0.0666)</t>
+          <t>(0.0539)</t>
         </is>
       </c>
       <c r="AO102" s="2" t="inlineStr">
         <is>
-          <t>(0.0672)</t>
+          <t>(0.0651)</t>
         </is>
       </c>
       <c r="AP102" s="2" t="inlineStr">
         <is>
-          <t>(0.0643)</t>
+          <t>(0.0519)</t>
         </is>
       </c>
       <c r="AQ102" s="2" t="inlineStr">
         <is>
-          <t>(0.0687)</t>
+          <t>(0.0550)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Region FE: North America</t>
+          <t>Region FE: Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>-0.2238***</t>
+          <t>0.2753***</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>-0.2559***</t>
+          <t>0.2544***</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>-0.3716***</t>
+          <t>0.2413***</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>-0.3793***</t>
+          <t>0.2082**</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-0.3766***</t>
+          <t>0.2191**</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-0.3946***</t>
+          <t>0.1933**</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>-0.2465***</t>
+          <t>0.2788***</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>-0.3449***</t>
+          <t>0.2500***</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>-0.3459***</t>
+          <t>0.2107**</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-0.3458***</t>
+          <t>0.2207**</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>-0.3544***</t>
+          <t>0.1818**</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-0.3314***</t>
+          <t>0.2365**</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-0.2831***</t>
+          <t>0.2268**</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-0.2571***</t>
+          <t>0.2656***</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>-0.3233***</t>
+          <t>0.1980**</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>-0.2685***</t>
+          <t>0.2636***</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>-0.3766***</t>
+          <t>0.2455***</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>-0.3809***</t>
+          <t>0.2098**</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>-0.3802***</t>
+          <t>0.2233**</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>-0.3841***</t>
+          <t>0.1730**</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>-0.3673***</t>
+          <t>0.2377***</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>-0.3282***</t>
+          <t>0.2330***</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>-0.3429***</t>
+          <t>0.2445***</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>-0.3795***</t>
+          <t>0.1994**</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
         <is>
-          <t>-0.3398***</t>
+          <t>0.1460</t>
         </is>
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>-0.4203***</t>
+          <t>0.1524*</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>-0.4184***</t>
+          <t>0.1370</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>-0.4167***</t>
+          <t>0.1514*</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>-0.4172***</t>
+          <t>0.1503*</t>
         </is>
       </c>
       <c r="AE103" s="2" t="inlineStr">
         <is>
-          <t>-0.4274***</t>
+          <t>0.1403</t>
         </is>
       </c>
       <c r="AF103" s="2" t="inlineStr">
         <is>
-          <t>-0.4115***</t>
+          <t>0.1479*</t>
         </is>
       </c>
       <c r="AG103" s="2" t="inlineStr">
         <is>
-          <t>-0.4316***</t>
+          <t>0.1469*</t>
         </is>
       </c>
       <c r="AH103" s="2" t="inlineStr">
         <is>
-          <t>-0.4243***</t>
+          <t>0.1430</t>
         </is>
       </c>
       <c r="AI103" s="2" t="inlineStr">
         <is>
-          <t>-0.3331***</t>
+          <t>0.1611*</t>
         </is>
       </c>
       <c r="AJ103" s="2" t="inlineStr">
         <is>
-          <t>-0.4156***</t>
+          <t>0.1683*</t>
         </is>
       </c>
       <c r="AK103" s="2" t="inlineStr">
         <is>
-          <t>-0.4148***</t>
+          <t>0.1582*</t>
         </is>
       </c>
       <c r="AL103" s="2" t="inlineStr">
         <is>
-          <t>-0.4127***</t>
+          <t>0.1726*</t>
         </is>
       </c>
       <c r="AM103" s="2" t="inlineStr">
         <is>
-          <t>-0.4150***</t>
+          <t>0.1684*</t>
         </is>
       </c>
       <c r="AN103" s="2" t="inlineStr">
         <is>
-          <t>-0.4175***</t>
+          <t>0.1654*</t>
         </is>
       </c>
       <c r="AO103" s="2" t="inlineStr">
         <is>
-          <t>-0.4143***</t>
+          <t>0.1723*</t>
         </is>
       </c>
       <c r="AP103" s="2" t="inlineStr">
         <is>
-          <t>-0.4288***</t>
+          <t>0.1766**</t>
         </is>
       </c>
       <c r="AQ103" s="2" t="inlineStr">
         <is>
-          <t>-0.4177***</t>
+          <t>0.1669*</t>
         </is>
       </c>
     </row>
@@ -19279,429 +19279,429 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>(0.0571)</t>
+          <t>(0.0919)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>(0.0607)</t>
+          <t>(0.0899)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>(0.0734)</t>
+          <t>(0.0874)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>(0.0739)</t>
+          <t>(0.0878)</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>(0.0743)</t>
+          <t>(0.0912)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>(0.0765)</t>
+          <t>(0.0910)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>(0.0797)</t>
+          <t>(0.0911)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>(0.0855)</t>
+          <t>(0.0906)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>(0.0845)</t>
+          <t>(0.0898)</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>(0.0846)</t>
+          <t>(0.0926)</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>(0.0843)</t>
+          <t>(0.0908)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>(0.0878)</t>
+          <t>(0.0938)</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>(0.0939)</t>
+          <t>(0.0912)</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>(0.0930)</t>
+          <t>(0.0953)</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>(0.0891)</t>
+          <t>(0.0961)</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>(0.0699)</t>
+          <t>(0.0876)</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>(0.0797)</t>
+          <t>(0.0853)</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>(0.0799)</t>
+          <t>(0.0865)</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>(0.0804)</t>
+          <t>(0.0892)</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>(0.0826)</t>
+          <t>(0.0879)</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>(0.0825)</t>
+          <t>(0.0850)</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
+          <t>(0.0866)</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0899)</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0896)</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0908)</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0901)</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0886)</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0906)</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0909)</t>
+        </is>
+      </c>
+      <c r="AE104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0905)</t>
+        </is>
+      </c>
+      <c r="AF104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0876)</t>
+        </is>
+      </c>
+      <c r="AG104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0859)</t>
+        </is>
+      </c>
+      <c r="AH104" s="2" t="inlineStr">
+        <is>
+          <t>(0.0905)</t>
+        </is>
+      </c>
+      <c r="AI104" s="2" t="inlineStr">
+        <is>
           <t>(0.0913)</t>
         </is>
       </c>
-      <c r="X104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0885)</t>
-        </is>
-      </c>
-      <c r="Y104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0807)</t>
-        </is>
-      </c>
-      <c r="Z104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0592)</t>
-        </is>
-      </c>
-      <c r="AA104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0705)</t>
-        </is>
-      </c>
-      <c r="AB104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0717)</t>
-        </is>
-      </c>
-      <c r="AC104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0724)</t>
-        </is>
-      </c>
-      <c r="AD104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0733)</t>
-        </is>
-      </c>
-      <c r="AE104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0698)</t>
-        </is>
-      </c>
-      <c r="AF104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0671)</t>
-        </is>
-      </c>
-      <c r="AG104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0644)</t>
-        </is>
-      </c>
-      <c r="AH104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0702)</t>
-        </is>
-      </c>
-      <c r="AI104" s="2" t="inlineStr">
-        <is>
-          <t>(0.0602)</t>
-        </is>
-      </c>
       <c r="AJ104" s="2" t="inlineStr">
         <is>
-          <t>(0.0713)</t>
+          <t>(0.0908)</t>
         </is>
       </c>
       <c r="AK104" s="2" t="inlineStr">
         <is>
-          <t>(0.0723)</t>
+          <t>(0.0897)</t>
         </is>
       </c>
       <c r="AL104" s="2" t="inlineStr">
         <is>
-          <t>(0.0729)</t>
+          <t>(0.0919)</t>
         </is>
       </c>
       <c r="AM104" s="2" t="inlineStr">
         <is>
-          <t>(0.0744)</t>
+          <t>(0.0922)</t>
         </is>
       </c>
       <c r="AN104" s="2" t="inlineStr">
         <is>
-          <t>(0.0711)</t>
+          <t>(0.0907)</t>
         </is>
       </c>
       <c r="AO104" s="2" t="inlineStr">
         <is>
-          <t>(0.0709)</t>
+          <t>(0.0903)</t>
         </is>
       </c>
       <c r="AP104" s="2" t="inlineStr">
         <is>
-          <t>(0.0677)</t>
+          <t>(0.0894)</t>
         </is>
       </c>
       <c r="AQ104" s="2" t="inlineStr">
         <is>
-          <t>(0.0729)</t>
+          <t>(0.0917)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Region FE: Sub-Saharan Africa</t>
+          <t>Region FE: South Asia</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>-0.0672</t>
+          <t>0.0815</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>-0.0249</t>
+          <t>0.0755</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-0.0408</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>-0.0495</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-0.0453</t>
+          <t>0.1285</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-0.0587</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>0.0209</t>
+          <t>0.0730</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>-0.0069</t>
+          <t>0.1033</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>-0.0172</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-0.0139</t>
+          <t>0.1278</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>-0.0376</t>
+          <t>0.1221</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-0.0312</t>
+          <t>0.0896</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-0.0530</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-0.0117</t>
+          <t>0.0888</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>-0.0397</t>
+          <t>0.0873</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>-0.0178</t>
+          <t>0.0703</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>-0.0374</t>
+          <t>0.1038</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>-0.0484</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>-0.0424</t>
+          <t>0.1265</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>-0.0718</t>
+          <t>0.1158</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>-0.0419</t>
+          <t>0.0923</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>-0.0400</t>
+          <t>0.0687</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>-0.0323</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>-0.0642</t>
+          <t>0.0890</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
         <is>
-          <t>-0.1066**</t>
+          <t>-0.0274</t>
         </is>
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>-0.1069*</t>
+          <t>0.0114</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>-0.1049*</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>-0.1013*</t>
+          <t>0.0370</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>-0.1008*</t>
+          <t>0.0387</t>
         </is>
       </c>
       <c r="AE105" s="2" t="inlineStr">
         <is>
-          <t>-0.0880</t>
+          <t>0.0076</t>
         </is>
       </c>
       <c r="AF105" s="2" t="inlineStr">
         <is>
-          <t>-0.0644</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="AG105" s="2" t="inlineStr">
         <is>
-          <t>-0.0720</t>
+          <t>0.0091</t>
         </is>
       </c>
       <c r="AH105" s="2" t="inlineStr">
         <is>
-          <t>-0.0983*</t>
+          <t>-0.0064</t>
         </is>
       </c>
       <c r="AI105" s="2" t="inlineStr">
         <is>
-          <t>-0.0904*</t>
+          <t>0.0007</t>
         </is>
       </c>
       <c r="AJ105" s="2" t="inlineStr">
         <is>
-          <t>-0.0910*</t>
+          <t>0.0413</t>
         </is>
       </c>
       <c r="AK105" s="2" t="inlineStr">
         <is>
-          <t>-0.0901*</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="AL105" s="2" t="inlineStr">
         <is>
-          <t>-0.0857</t>
+          <t>0.0603</t>
         </is>
       </c>
       <c r="AM105" s="2" t="inlineStr">
         <is>
-          <t>-0.0849</t>
+          <t>0.0642</t>
         </is>
       </c>
       <c r="AN105" s="2" t="inlineStr">
         <is>
-          <t>-0.0739</t>
+          <t>0.0462</t>
         </is>
       </c>
       <c r="AO105" s="2" t="inlineStr">
         <is>
-          <t>-0.0668</t>
+          <t>0.0561</t>
         </is>
       </c>
       <c r="AP105" s="2" t="inlineStr">
         <is>
-          <t>-0.0487</t>
+          <t>0.0544</t>
         </is>
       </c>
       <c r="AQ105" s="2" t="inlineStr">
         <is>
-          <t>-0.0916*</t>
+          <t>0.0410</t>
         </is>
       </c>
     </row>
@@ -19709,429 +19709,429 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(0.0546)</t>
+          <t>(0.1161)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>(0.0542)</t>
+          <t>(0.1120)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>(0.0543)</t>
+          <t>(0.1050)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>(0.0538)</t>
+          <t>(0.1075)</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>(0.0545)</t>
+          <t>(0.1073)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>(0.0526)</t>
+          <t>(0.1046)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>(0.0613)</t>
+          <t>(0.1150)</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>(0.0628)</t>
+          <t>(0.1072)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>(0.0629)</t>
+          <t>(0.1115)</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>(0.0627)</t>
+          <t>(0.1113)</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>(0.0631)</t>
+          <t>(0.1072)</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>(0.0614)</t>
+          <t>(0.1048)</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>(0.0638)</t>
+          <t>(0.1217)</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>(0.0602)</t>
+          <t>(0.1069)</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>(0.0615)</t>
+          <t>(0.1017)</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>(0.0532)</t>
+          <t>(0.1180)</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>(0.0534)</t>
+          <t>(0.1112)</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>(0.0543)</t>
+          <t>(0.1140)</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>(0.0543)</t>
+          <t>(0.1134)</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>(0.0551)</t>
+          <t>(0.1069)</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>(0.0516)</t>
+          <t>(0.1108)</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>(0.0514)</t>
+          <t>(0.1246)</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>(0.0522)</t>
+          <t>(0.1152)</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>(0.0544)</t>
+          <t>(0.1031)</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
         <is>
-          <t>(0.0534)</t>
+          <t>(0.1136)</t>
         </is>
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>(0.0552)</t>
+          <t>(0.1080)</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>(0.0549)</t>
+          <t>(0.1127)</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>(0.0546)</t>
+          <t>(0.1110)</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>(0.0543)</t>
+          <t>(0.1118)</t>
         </is>
       </c>
       <c r="AE106" s="2" t="inlineStr">
         <is>
-          <t>(0.0572)</t>
+          <t>(0.1057)</t>
         </is>
       </c>
       <c r="AF106" s="2" t="inlineStr">
         <is>
-          <t>(0.0614)</t>
+          <t>(0.1097)</t>
         </is>
       </c>
       <c r="AG106" s="2" t="inlineStr">
         <is>
-          <t>(0.0515)</t>
+          <t>(0.1003)</t>
         </is>
       </c>
       <c r="AH106" s="2" t="inlineStr">
         <is>
-          <t>(0.0526)</t>
+          <t>(0.0926)</t>
         </is>
       </c>
       <c r="AI106" s="2" t="inlineStr">
         <is>
-          <t>(0.0529)</t>
+          <t>(0.1259)</t>
         </is>
       </c>
       <c r="AJ106" s="2" t="inlineStr">
         <is>
-          <t>(0.0531)</t>
+          <t>(0.1209)</t>
         </is>
       </c>
       <c r="AK106" s="2" t="inlineStr">
         <is>
-          <t>(0.0529)</t>
+          <t>(0.1251)</t>
         </is>
       </c>
       <c r="AL106" s="2" t="inlineStr">
         <is>
-          <t>(0.0530)</t>
+          <t>(0.1238)</t>
         </is>
       </c>
       <c r="AM106" s="2" t="inlineStr">
         <is>
-          <t>(0.0523)</t>
+          <t>(0.1229)</t>
         </is>
       </c>
       <c r="AN106" s="2" t="inlineStr">
         <is>
-          <t>(0.0539)</t>
+          <t>(0.1212)</t>
         </is>
       </c>
       <c r="AO106" s="2" t="inlineStr">
         <is>
-          <t>(0.0651)</t>
+          <t>(0.1241)</t>
         </is>
       </c>
       <c r="AP106" s="2" t="inlineStr">
         <is>
-          <t>(0.0519)</t>
+          <t>(0.1202)</t>
         </is>
       </c>
       <c r="AQ106" s="2" t="inlineStr">
         <is>
-          <t>(0.0550)</t>
+          <t>(0.1177)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Region FE: South Asia</t>
+          <t>Region FE: North America</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>0.0815</t>
+          <t>-0.2238***</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>0.0755</t>
+          <t>-0.2559***</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>-0.3716***</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>-0.3793***</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>-0.3766***</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>-0.3946***</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>0.0730</t>
+          <t>-0.2465***</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>0.1033</t>
+          <t>-0.3449***</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>-0.3459***</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0.1278</t>
+          <t>-0.3458***</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>0.1221</t>
+          <t>-0.3544***</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0.0896</t>
+          <t>-0.3314***</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>-0.2831***</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0.0888</t>
+          <t>-0.2571***</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>0.0873</t>
+          <t>-0.3233***</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>0.0703</t>
+          <t>-0.2685***</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>0.1038</t>
+          <t>-0.3766***</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>0.1248</t>
+          <t>-0.3809***</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>0.1265</t>
+          <t>-0.3802***</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
         <is>
-          <t>0.1158</t>
+          <t>-0.3841***</t>
         </is>
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>0.0923</t>
+          <t>-0.3673***</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>0.0687</t>
+          <t>-0.3282***</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>-0.3429***</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>0.0890</t>
+          <t>-0.3795***</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
         <is>
-          <t>-0.0274</t>
+          <t>-0.3398***</t>
         </is>
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>0.0114</t>
+          <t>-0.4203***</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>-0.4184***</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>0.0370</t>
+          <t>-0.4167***</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>0.0387</t>
+          <t>-0.4172***</t>
         </is>
       </c>
       <c r="AE107" s="2" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>-0.4274***</t>
         </is>
       </c>
       <c r="AF107" s="2" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>-0.4115***</t>
         </is>
       </c>
       <c r="AG107" s="2" t="inlineStr">
         <is>
-          <t>0.0091</t>
+          <t>-0.4316***</t>
         </is>
       </c>
       <c r="AH107" s="2" t="inlineStr">
         <is>
-          <t>-0.0064</t>
+          <t>-0.4243***</t>
         </is>
       </c>
       <c r="AI107" s="2" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.3331***</t>
         </is>
       </c>
       <c r="AJ107" s="2" t="inlineStr">
         <is>
-          <t>0.0413</t>
+          <t>-0.4156***</t>
         </is>
       </c>
       <c r="AK107" s="2" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>-0.4148***</t>
         </is>
       </c>
       <c r="AL107" s="2" t="inlineStr">
         <is>
-          <t>0.0603</t>
+          <t>-0.4127***</t>
         </is>
       </c>
       <c r="AM107" s="2" t="inlineStr">
         <is>
-          <t>0.0642</t>
+          <t>-0.4150***</t>
         </is>
       </c>
       <c r="AN107" s="2" t="inlineStr">
         <is>
-          <t>0.0462</t>
+          <t>-0.4175***</t>
         </is>
       </c>
       <c r="AO107" s="2" t="inlineStr">
         <is>
-          <t>0.0561</t>
+          <t>-0.4143***</t>
         </is>
       </c>
       <c r="AP107" s="2" t="inlineStr">
         <is>
-          <t>0.0544</t>
+          <t>-0.4288***</t>
         </is>
       </c>
       <c r="AQ107" s="2" t="inlineStr">
         <is>
-          <t>0.0410</t>
+          <t>-0.4177***</t>
         </is>
       </c>
     </row>
@@ -20139,212 +20139,212 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>(0.1161)</t>
+          <t>(0.0571)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>(0.1120)</t>
+          <t>(0.0607)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>(0.1050)</t>
+          <t>(0.0734)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>(0.1075)</t>
+          <t>(0.0739)</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>(0.1073)</t>
+          <t>(0.0743)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>(0.1046)</t>
+          <t>(0.0765)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>(0.1150)</t>
+          <t>(0.0797)</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>(0.1072)</t>
+          <t>(0.0855)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>(0.1115)</t>
+          <t>(0.0845)</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>(0.1113)</t>
+          <t>(0.0846)</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>(0.1072)</t>
+          <t>(0.0843)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>(0.1048)</t>
+          <t>(0.0878)</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>(0.1217)</t>
+          <t>(0.0939)</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>(0.1069)</t>
+          <t>(0.0930)</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>(0.1017)</t>
+          <t>(0.0891)</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>(0.1180)</t>
+          <t>(0.0699)</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>(0.1112)</t>
+          <t>(0.0797)</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>(0.1140)</t>
+          <t>(0.0799)</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>(0.1134)</t>
+          <t>(0.0804)</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>(0.1069)</t>
+          <t>(0.0826)</t>
         </is>
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>(0.1108)</t>
+          <t>(0.0825)</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>(0.1246)</t>
+          <t>(0.0913)</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>(0.1152)</t>
+          <t>(0.0885)</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>(0.1031)</t>
+          <t>(0.0807)</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
         <is>
-          <t>(0.1136)</t>
+          <t>(0.0592)</t>
         </is>
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>(0.1080)</t>
+          <t>(0.0705)</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>(0.1127)</t>
+          <t>(0.0717)</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>(0.1110)</t>
+          <t>(0.0724)</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>(0.1118)</t>
+          <t>(0.0733)</t>
         </is>
       </c>
       <c r="AE108" s="2" t="inlineStr">
         <is>
-          <t>(0.1057)</t>
+          <t>(0.0698)</t>
         </is>
       </c>
       <c r="AF108" s="2" t="inlineStr">
         <is>
-          <t>(0.1097)</t>
+          <t>(0.0671)</t>
         </is>
       </c>
       <c r="AG108" s="2" t="inlineStr">
         <is>
-          <t>(0.1003)</t>
+          <t>(0.0644)</t>
         </is>
       </c>
       <c r="AH108" s="2" t="inlineStr">
         <is>
-          <t>(0.0926)</t>
+          <t>(0.0702)</t>
         </is>
       </c>
       <c r="AI108" s="2" t="inlineStr">
         <is>
-          <t>(0.1259)</t>
+          <t>(0.0602)</t>
         </is>
       </c>
       <c r="AJ108" s="2" t="inlineStr">
         <is>
-          <t>(0.1209)</t>
+          <t>(0.0713)</t>
         </is>
       </c>
       <c r="AK108" s="2" t="inlineStr">
         <is>
-          <t>(0.1251)</t>
+          <t>(0.0723)</t>
         </is>
       </c>
       <c r="AL108" s="2" t="inlineStr">
         <is>
-          <t>(0.1238)</t>
+          <t>(0.0729)</t>
         </is>
       </c>
       <c r="AM108" s="2" t="inlineStr">
         <is>
-          <t>(0.1229)</t>
+          <t>(0.0744)</t>
         </is>
       </c>
       <c r="AN108" s="2" t="inlineStr">
         <is>
-          <t>(0.1212)</t>
+          <t>(0.0711)</t>
         </is>
       </c>
       <c r="AO108" s="2" t="inlineStr">
         <is>
-          <t>(0.1241)</t>
+          <t>(0.0709)</t>
         </is>
       </c>
       <c r="AP108" s="2" t="inlineStr">
         <is>
-          <t>(0.1202)</t>
+          <t>(0.0677)</t>
         </is>
       </c>
       <c r="AQ108" s="2" t="inlineStr">
         <is>
-          <t>(0.1177)</t>
+          <t>(0.0729)</t>
         </is>
       </c>
     </row>
